--- a/docs/downloads/2026-10-30/bursa-report-2026-10-30.xlsx
+++ b/docs/downloads/2026-10-30/bursa-report-2026-10-30.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-30" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-30'!$A$1:$M$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-30'!$A$1:$M$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.075</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.0625</v>
+        <v>-0.125</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>37758900</v>
+        <v>141743500</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.1</v>
+        <v>0.39</v>
       </c>
       <c r="H2" t="n">
-        <v>34.92</v>
+        <v>33.82</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.53</v>
+        <v>0.24</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-0.0185</v>
+        <v>-0.5556</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>3646600</v>
+        <v>29993800</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.15</v>
+        <v>1.22</v>
       </c>
       <c r="H3" t="n">
-        <v>31.93</v>
+        <v>16.55</v>
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.646</v>
+        <v>0.619</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.581</v>
+        <v>0.575</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -633,28 +633,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.335</v>
+        <v>0.145</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-0.0147</v>
+        <v>-0.0333</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>2111100</v>
+        <v>23719400</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.03</v>
+        <v>0.49</v>
       </c>
       <c r="H4" t="n">
-        <v>57.95</v>
+        <v>44.67</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -662,10 +662,10 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.325</v>
+        <v>0.157</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.275</v>
+        <v>0.15</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -687,19 +687,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>0.0405</v>
+        <v>0.25</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>-0.3243</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1734700</v>
+        <v>16578900</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.04</v>
+        <v>0.4</v>
       </c>
       <c r="H5" t="n">
-        <v>45.89</v>
+        <v>30.29</v>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.425</v>
+        <v>0.412</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.346</v>
+        <v>0.344</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,39 +723,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.36</v>
+        <v>0.335</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.0147</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1594700</v>
+        <v>9969800</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.66</v>
+        <v>0.14</v>
       </c>
       <c r="H6" t="n">
-        <v>39.95</v>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.95</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.379</v>
+        <v>0.325</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.385</v>
+        <v>0.275</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,28 +768,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>EWICAP</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>-0.025</v>
+        <v>0.145</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>0.0741</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>981100</v>
+        <v>6905500</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.05</v>
+        <v>5.83</v>
       </c>
       <c r="H7" t="n">
-        <v>53.16</v>
+        <v>52.26</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.577</v>
+        <v>0.138</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.554</v>
+        <v>0.162</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,28 +813,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>BINTAI</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0</v>
+        <v>0.075</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-0.0625</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>695600</v>
+        <v>6024500</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.28</v>
+        <v>3.08</v>
       </c>
       <c r="H8" t="n">
-        <v>59.85</v>
+        <v>53.8</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.643</v>
+        <v>0.073</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.632</v>
+        <v>0.073</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -858,39 +858,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>-0.0135</v>
+        <v>0.49</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>526100</v>
+        <v>5553000</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.02</v>
+        <v>0.25</v>
       </c>
       <c r="H9" t="n">
-        <v>63.55</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.97</v>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.049</v>
+        <v>0.45</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1.852</v>
+        <v>0.402</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -903,45 +903,2007 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>0.0949</v>
+        <v>0.0101</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>525200</v>
+        <v>4992900</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="H10" t="n">
-        <v>50.38</v>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>73.23</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.075</v>
+        <v>0.901</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2.679</v>
+        <v>0.789</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>4937900</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H11" t="n">
+        <v>62.76</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>-0.03700000000000001</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>3963600</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H12" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0478</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NWEBHD</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>3635700</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>3578000</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H14" t="n">
+        <v>62.76</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>2.048</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>1.851</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>5318</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DXN</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>3333800</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H15" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>9113</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ICONIC</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>3037200</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H16" t="n">
+        <v>70.39</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0476</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>0.04650000000000001</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>2829100</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H17" t="n">
+        <v>51.19</v>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0024</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>JAG</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>2552600</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H18" t="n">
+        <v>59.17</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>2368400</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>53.16</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0328</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3REN</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.0267</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>2217400</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H20" t="n">
+        <v>41.83</v>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>2084000</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H21" t="n">
+        <v>50.94</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-0.1058</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>1877200</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>3.022</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>2.668</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>1867500</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H23" t="n">
+        <v>69.29000000000001</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>1.142</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>1.076</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5932</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BPURI</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>1787200</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H24" t="n">
+        <v>45.53</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.0171</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>1775800</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>44.03</v>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>0.0155</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>1742200</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H26" t="n">
+        <v>67.29000000000001</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>1.213</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>1.164</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AVANGAAD</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1740000</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H27" t="n">
+        <v>49.15</v>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>1729100</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H28" t="n">
+        <v>55.59</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.0222</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>1419000</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H29" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>-0.0175</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1405100</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H30" t="n">
+        <v>48.32</v>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1352800</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H31" t="n">
+        <v>56.71</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>2.117</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>-0.0231</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>1208000</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>2.574</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1098100</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H33" t="n">
+        <v>73.44</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1086300</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>53.09</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>5078</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>M&amp;G</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>1006400</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H35" t="n">
+        <v>39.38</v>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>-0.0159</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>986800</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H36" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>-0.0148</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>902300</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H37" t="n">
+        <v>61.63</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>VLB</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>877800</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H38" t="n">
+        <v>50.77</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>869000</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H39" t="n">
+        <v>59.85</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>-0.0379</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>859100</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H40" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>-0.0224</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>834100</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H41" t="n">
+        <v>51.14</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>2.612</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>2.597</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>804000</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H42" t="n">
+        <v>53.08</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>4.904</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>4.804</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>798800</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H43" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>779500</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H44" t="n">
+        <v>28.89</v>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>7.242</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>7.567</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>769900</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H45" t="n">
+        <v>67.52</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>2.187</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>2.219</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0477</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ECOSYS</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>-0.0276</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>672600</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>-0.0248</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>661500</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H47" t="n">
+        <v>56.51</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>6.472</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>6.075</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>647500</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H48" t="n">
+        <v>48.55</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>5.353</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>7245</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CITAGLB</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>638100</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="H49" t="n">
+        <v>67.01000000000001</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>1.064</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>-0.0063</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>634600</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H50" t="n">
+        <v>46</v>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>4.726</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>4.788</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>561200</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H51" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>3.853</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>3.419</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="E52" s="9" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>538500</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H52" t="n">
+        <v>52.48</v>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>2.297</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>-0.0253</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>523000</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H53" t="n">
+        <v>51.03</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>3.849</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>3.784</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>508000</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H54" t="n">
+        <v>52.98</v>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M10"/>
+  <autoFilter ref="A1:M54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-30/bursa-report-2026-10-30.xlsx
+++ b/docs/downloads/2026-10-30/bursa-report-2026-10-30.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-30" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-30'!$A$1:$M$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-30'!$A$1:$M$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>-0.125</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>141743500</v>
+        <v>174203300</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.39</v>
+        <v>0.48</v>
       </c>
       <c r="H2" t="n">
         <v>33.82</v>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.24</v>
+        <v>0.33</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>-0.5556</v>
+        <v>-0.3889</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>29993800</v>
+        <v>47557800</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>1.22</v>
+        <v>1.93</v>
       </c>
       <c r="H3" t="n">
-        <v>16.55</v>
+        <v>19.46</v>
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.619</v>
+        <v>0.627</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.575</v>
+        <v>0.577</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -642,19 +642,19 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.145</v>
+        <v>0.14</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>-0.0333</v>
+        <v>-0.0667</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>23719400</v>
+        <v>33377700</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.49</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>44.67</v>
+        <v>42.73</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -687,19 +687,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.25</v>
+        <v>0.215</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-0.3243</v>
+        <v>-0.4189</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>16578900</v>
+        <v>28809500</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.4</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>30.29</v>
+        <v>27.88</v>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.412</v>
+        <v>0.408</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -738,10 +738,10 @@
         <v>-0.0147</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9969800</v>
+        <v>11051000</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H6" t="n">
         <v>57.95</v>
@@ -768,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EWICAP</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.145</v>
+        <v>0.49</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>0.0741</v>
+        <v>0.0208</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>6905500</v>
+        <v>10803500</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>5.83</v>
+        <v>0.48</v>
       </c>
       <c r="H7" t="n">
-        <v>52.26</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.97</v>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.138</v>
+        <v>0.45</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.162</v>
+        <v>0.402</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,28 +813,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BINTAI</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>-0.0625</v>
+        <v>0.995</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0.0051</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6024500</v>
+        <v>9224700</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>3.08</v>
+        <v>0.11</v>
       </c>
       <c r="H8" t="n">
-        <v>53.8</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.073</v>
+        <v>0.9</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.073</v>
+        <v>0.789</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -858,39 +858,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>0.0208</v>
+        <v>0.16</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-0.0857</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5553000</v>
+        <v>7469900</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.25</v>
+        <v>0.79</v>
       </c>
       <c r="H9" t="n">
-        <v>65.97</v>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.77</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.45</v>
+        <v>0.143</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.402</v>
+        <v>0.121</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -903,28 +903,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>0.0101</v>
+        <v>0.39</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4992900</v>
+        <v>7377600</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.06</v>
+        <v>0.51</v>
       </c>
       <c r="H10" t="n">
-        <v>73.23</v>
+        <v>35.76</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.901</v>
+        <v>0.446</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.789</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -948,28 +948,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>EWICAP</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1.04</v>
+        <v>0.145</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>0.0196</v>
+        <v>0.0741</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4937900</v>
+        <v>7100800</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.67</v>
+        <v>5.99</v>
       </c>
       <c r="H11" t="n">
-        <v>62.76</v>
+        <v>52.26</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.875</v>
+        <v>0.138</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.675</v>
+        <v>0.162</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -993,28 +993,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.39</v>
+        <v>2.17</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.0269</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3963600</v>
+        <v>7099800</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="H12" t="n">
-        <v>35.76</v>
+        <v>61.25</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
@@ -1022,10 +1022,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.446</v>
+        <v>2.046</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.851</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1038,33 +1038,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>BINTAI</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.195</v>
+        <v>0.075</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0.025</v>
+        <v>-0.0625</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3635700</v>
+        <v>6194500</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="2" t="n"/>
+        <v>3.17</v>
+      </c>
+      <c r="H13" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.073</v>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
     </row>
@@ -1076,28 +1083,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2.19</v>
+        <v>0.99</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-0.0179</v>
+        <v>-0.0294</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3578000</v>
+        <v>5985300</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.12</v>
+        <v>0.82</v>
       </c>
       <c r="H14" t="n">
-        <v>62.76</v>
+        <v>59.79</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
@@ -1105,10 +1112,10 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.048</v>
+        <v>0.87</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1.851</v>
+        <v>0.674</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1121,39 +1128,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>0.0108</v>
+        <v>0.295</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3333800</v>
+        <v>5960000</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="H15" t="n">
-        <v>59.25</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.463</v>
+        <v>0.295</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.462</v>
+        <v>0.295</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1175,19 +1182,19 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>0</v>
+        <v>0.12</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3037200</v>
+        <v>4327200</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="H16" t="n">
-        <v>70.39</v>
+        <v>73.88</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
@@ -1195,7 +1202,7 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.104</v>
+        <v>0.105</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0.08799999999999999</v>
@@ -1211,36 +1218,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2829100</v>
+        <v>3794400</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="H17" t="n">
-        <v>51.19</v>
+        <v>39.38</v>
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
+      <c r="J17" s="2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0.304</v>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
     </row>
@@ -1252,40 +1263,33 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>0.0133</v>
+        <v>0.19</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-0.05</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2552600</v>
+        <v>3671200</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="H18" t="n">
-        <v>59.17</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>0.37</v>
-      </c>
+        <v>0.16</v>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
     </row>
@@ -1297,28 +1301,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-0.025</v>
+        <v>0.775</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2368400</v>
+        <v>3662400</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="H19" t="n">
-        <v>53.16</v>
+        <v>50.94</v>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
@@ -1326,10 +1330,10 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.577</v>
+        <v>0.774</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.554</v>
+        <v>0.775</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1342,39 +1346,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>0129</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>SRIDGE</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>-0.0267</v>
+        <v>0.12</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>0.09089999999999999</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2217400</v>
+        <v>3629600</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.92</v>
+        <v>3.24</v>
       </c>
       <c r="H20" t="n">
-        <v>41.83</v>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.02</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.38</v>
+        <v>0.118</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.385</v>
+        <v>0.13</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1387,39 +1391,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0</v>
+        <v>4.71</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2084000</v>
+        <v>3554400</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="H21" t="n">
-        <v>50.94</v>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.94</v>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.774</v>
+        <v>4.727</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.775</v>
+        <v>4.788</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1432,40 +1436,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>-0.1058</v>
+        <v>0.225</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>0.04650000000000001</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1877200</v>
+        <v>3532900</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="H22" t="n">
-        <v>31.63</v>
+        <v>51.19</v>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J22" s="2" t="n">
-        <v>3.022</v>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>2.668</v>
-      </c>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
     </row>
@@ -1477,28 +1477,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>0.0161</v>
+        <v>0.585</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1867500</v>
+        <v>3509100</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H23" t="n">
-        <v>69.29000000000001</v>
+        <v>53.16</v>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.142</v>
+        <v>0.577</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1.076</v>
+        <v>0.554</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1522,28 +1522,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>0</v>
+        <v>0.38</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1787200</v>
+        <v>3447600</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1.42</v>
+        <v>0.51</v>
       </c>
       <c r="H24" t="n">
-        <v>45.53</v>
+        <v>59.17</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
@@ -1551,10 +1551,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.223</v>
+        <v>0.374</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.229</v>
+        <v>0.37</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1567,39 +1567,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>-0.0171</v>
+        <v>0.47</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1775800</v>
+        <v>3376800</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="H25" t="n">
-        <v>44.03</v>
-      </c>
-      <c r="I25" s="8" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.25</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.601</v>
+        <v>0.463</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.619</v>
+        <v>0.462</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1612,28 +1612,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>0.0155</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1742200</v>
+        <v>2901100</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H26" t="n">
-        <v>67.29000000000001</v>
+        <v>68.44</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.213</v>
+        <v>1.141</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1.164</v>
+        <v>1.076</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1657,39 +1657,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0</v>
+        <v>1.3</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1740000</v>
+        <v>2826900</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.5</v>
+        <v>0.41</v>
       </c>
       <c r="H27" t="n">
-        <v>49.15</v>
-      </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.3</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.295</v>
+        <v>1.212</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.295</v>
+        <v>1.164</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1702,39 +1702,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>0.0122</v>
+        <v>0.36</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1729100</v>
+        <v>2806500</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.15</v>
+        <v>1.16</v>
       </c>
       <c r="H28" t="n">
-        <v>55.59</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.95</v>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.404</v>
+        <v>0.379</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.386</v>
+        <v>0.385</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1747,39 +1747,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.44</v>
+        <v>2.22</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.0222</v>
+        <v>-0.1898</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1419000</v>
+        <v>2774800</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.04</v>
+        <v>0.83</v>
       </c>
       <c r="H29" t="n">
-        <v>44.62</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.34</v>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.452</v>
+        <v>3</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.47</v>
+        <v>2.663</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1792,39 +1792,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>-0.0175</v>
+        <v>0.82</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1405100</v>
+        <v>2608300</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="H30" t="n">
-        <v>48.32</v>
-      </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.09</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.283</v>
+        <v>0.819</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.279</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1837,28 +1837,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>0.0185</v>
+        <v>0.865</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1352800</v>
+        <v>2581900</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H31" t="n">
-        <v>56.71</v>
+        <v>47.49</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>2.117</v>
+        <v>0.867</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>2.225</v>
+        <v>0.868</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1891,19 +1891,19 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>-0.0231</v>
+        <v>-0.0269</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1208000</v>
+        <v>2543700</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="H32" t="n">
-        <v>46.53</v>
+        <v>45.91</v>
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>2.59</v>
+        <v>2.589</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>2.574</v>
@@ -1927,28 +1927,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.845</v>
+        <v>0.415</v>
       </c>
       <c r="E33" s="9" t="n">
-        <v>0.0181</v>
+        <v>0.0122</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1098100</v>
+        <v>2286500</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="H33" t="n">
-        <v>73.44</v>
+        <v>55.59</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.404</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.785</v>
+        <v>0.386</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1972,28 +1972,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>0</v>
+        <v>2.17</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>0.0046</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1086300</v>
+        <v>2071100</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="H34" t="n">
-        <v>53.09</v>
+        <v>54.25</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.819</v>
+        <v>2.114</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>2.224</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2017,28 +2017,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0</v>
+        <v>0.57</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>-0.0256</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1006400</v>
+        <v>2024400</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="H35" t="n">
-        <v>39.38</v>
+        <v>43.28</v>
       </c>
       <c r="I35" s="8" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.305</v>
+        <v>0.601</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.304</v>
+        <v>0.619</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2062,28 +2062,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.93</v>
+        <v>0.27</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-0.0159</v>
+        <v>-0.0526</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>986800</v>
+        <v>1975100</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="H36" t="n">
-        <v>41.3</v>
+        <v>44.52</v>
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.982</v>
+        <v>0.282</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.997</v>
+        <v>0.279</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2107,28 +2107,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>-0.0148</v>
+        <v>4</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>0.0336</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>902300</v>
+        <v>1921700</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="H37" t="n">
-        <v>61.63</v>
+        <v>57.93</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2136,10 +2136,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.616</v>
+        <v>3.859</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.589</v>
+        <v>3.42</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2152,28 +2152,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0</v>
+        <v>0.445</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>-0.0111</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>877800</v>
+        <v>1854600</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.44</v>
+        <v>0.06</v>
       </c>
       <c r="H38" t="n">
-        <v>50.77</v>
+        <v>46.04</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.904</v>
+        <v>0.452</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.899</v>
+        <v>0.47</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2197,28 +2197,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.655</v>
+        <v>0.22</v>
       </c>
       <c r="E39" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>869000</v>
+        <v>1787300</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.35</v>
+        <v>1.42</v>
       </c>
       <c r="H39" t="n">
-        <v>59.85</v>
+        <v>45.53</v>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.643</v>
+        <v>0.223</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.632</v>
+        <v>0.229</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2242,39 +2242,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>-0.0379</v>
+        <v>6.91</v>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>0.0029</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>859100</v>
+        <v>1614500</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
       <c r="H40" t="n">
-        <v>58.75</v>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.59</v>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.594</v>
+        <v>7.239</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.503</v>
+        <v>7.566</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2287,39 +2287,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2.62</v>
+        <v>0.275</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>-0.0224</v>
+        <v>-0.0179</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>834100</v>
+        <v>1550700</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="H41" t="n">
-        <v>51.14</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.24</v>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.612</v>
+        <v>0.304</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>2.597</v>
+        <v>0.35</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2332,28 +2332,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>-0.014</v>
+        <v>0.905</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>804000</v>
+        <v>1532800</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.04</v>
+        <v>0.77</v>
       </c>
       <c r="H42" t="n">
-        <v>53.08</v>
+        <v>50.77</v>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>4.904</v>
+        <v>0.904</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>4.804</v>
+        <v>0.899</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2377,39 +2377,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>0</v>
+        <v>0.66</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>0.0076</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>798800</v>
+        <v>1531700</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.24</v>
+        <v>0.61</v>
       </c>
       <c r="H43" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.2</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.745</v>
+        <v>0.644</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.709</v>
+        <v>0.633</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2422,28 +2422,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="E44" s="9" t="n">
-        <v>0.0073</v>
+        <v>0.38</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>-0.0256</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>779500</v>
+        <v>1440700</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.05</v>
+        <v>0.27</v>
       </c>
       <c r="H44" t="n">
-        <v>28.89</v>
+        <v>36.29</v>
       </c>
       <c r="I44" s="8" t="inlineStr">
         <is>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>7.242</v>
+        <v>0.411</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>7.567</v>
+        <v>0.438</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2467,39 +2467,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="E45" s="9" t="n">
-        <v>0.0083</v>
+        <v>0.0263</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>769900</v>
+        <v>1428400</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="H45" t="n">
-        <v>67.52</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.49</v>
+      </c>
+      <c r="I45" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2.187</v>
+        <v>2.3</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2.219</v>
+        <v>2.231</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2512,33 +2512,40 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.705</v>
+        <v>0.655</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>-0.0276</v>
+        <v>-0.0296</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>672600</v>
+        <v>1398500</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I46" s="8" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="n"/>
+        <v>0.3</v>
+      </c>
+      <c r="H46" t="n">
+        <v>59.33</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0.589</v>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
     </row>
@@ -2550,39 +2557,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>-0.0248</v>
+        <v>0.38</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>661500</v>
+        <v>1393500</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.12</v>
+        <v>0.65</v>
       </c>
       <c r="H47" t="n">
-        <v>56.51</v>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.78</v>
+      </c>
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>6.472</v>
+        <v>0.428</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>6.075</v>
+        <v>0.45</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2595,28 +2602,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>5.34</v>
+        <v>0.835</v>
       </c>
       <c r="E48" s="9" t="n">
-        <v>0.0075</v>
+        <v>0.006</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>647500</v>
+        <v>1379600</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.04</v>
+        <v>0.28</v>
       </c>
       <c r="H48" t="n">
-        <v>48.55</v>
+        <v>69.81</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2624,10 +2631,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>5.353</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>5.54</v>
+        <v>0.785</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2640,28 +2647,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CITAGLB</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E49" s="9" t="n">
-        <v>0.045</v>
+        <v>2.08</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>638100</v>
+        <v>1325600</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>2.55</v>
+        <v>0.15</v>
       </c>
       <c r="H49" t="n">
-        <v>67.01000000000001</v>
+        <v>45.25</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2669,10 +2676,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.064</v>
+        <v>2.102</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1.051</v>
+        <v>2.116</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2685,39 +2692,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>4.7</v>
+        <v>6.66</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>-0.0063</v>
+        <v>-0.0292</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>634600</v>
+        <v>1253000</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.03</v>
+        <v>0.22</v>
       </c>
       <c r="H50" t="n">
-        <v>46</v>
-      </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.88</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>4.726</v>
+        <v>6.469</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>4.788</v>
+        <v>6.074</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2730,39 +2737,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="E51" s="9" t="n">
-        <v>0.0181</v>
+        <v>0.93</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>561200</v>
+        <v>1204800</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H51" t="n">
-        <v>56.3</v>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.3</v>
+      </c>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>3.853</v>
+        <v>0.982</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>3.419</v>
+        <v>0.997</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2775,39 +2782,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>2.31</v>
+        <v>0.345</v>
       </c>
       <c r="E52" s="9" t="n">
-        <v>0.0132</v>
+        <v>0.0455</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>538500</v>
+        <v>1167100</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
       <c r="H52" t="n">
-        <v>52.48</v>
-      </c>
-      <c r="I52" s="8" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.21</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>2.297</v>
+        <v>0.322</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>2.23</v>
+        <v>0.33</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2820,28 +2827,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>3.85</v>
+        <v>0.435</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>-0.0253</v>
+        <v>-0.0114</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>523000</v>
+        <v>1162800</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="H53" t="n">
-        <v>51.03</v>
+        <v>31.89</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2849,10 +2856,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>3.849</v>
+        <v>0.466</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>3.784</v>
+        <v>0.574</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2865,45 +2872,1478 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.78</v>
+        <v>4.91</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>-0.0064</v>
+        <v>-0.018</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>508000</v>
+        <v>1152200</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H54" t="n">
-        <v>52.98</v>
-      </c>
-      <c r="I54" s="8" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.76</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.772</v>
+        <v>4.902</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.771</v>
+        <v>4.803</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5099</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CAPITALA</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>-0.0227</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>1134200</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H55" t="n">
+        <v>40.59</v>
+      </c>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>1122800</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H56" t="n">
+        <v>57.95</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>1115400</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H57" t="n">
+        <v>39.64</v>
+      </c>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>2.702</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>2.749</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>1081000</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H58" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>5.539</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>-0.0319</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>1047000</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H59" t="n">
+        <v>43.61</v>
+      </c>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>1039600</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H60" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>6.327</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>6.568</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>1009900</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H61" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>997100</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H62" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0477</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ECOSYS</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>-0.0276</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>974500</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n"/>
+      <c r="K63" s="2" t="n"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>-0.0187</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>969700</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H64" t="n">
+        <v>52.05</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>2.613</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>2.597</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>900000</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H65" t="n">
+        <v>64.72</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>2.183</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>2.219</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>861800</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>40.23</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>1.272</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>1.459</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>826100</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H67" t="n">
+        <v>52.98</v>
+      </c>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>7245</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>CITAGLB</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E68" s="9" t="n">
+        <v>0.0541</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>797400</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="H68" t="n">
+        <v>68</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>1.064</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>1.051</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="7" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>-0.0177</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>778500</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H69" t="n">
+        <v>52.41</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>3.852</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>3.785</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>743700</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H70" t="n">
+        <v>47.36</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>9.993</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>10.088</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>-0.0299</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>672700</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H71" t="n">
+        <v>52.98</v>
+      </c>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>1.199</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>645700</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H72" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>2.992</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>2.883</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0198</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>GDB</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>645400</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H73" t="n">
+        <v>82.76000000000001</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>644100</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H74" t="n">
+        <v>39.53</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>1.551</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>1.807</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>-0.0331</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>603900</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H75" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>-0.0313</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>589200</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H76" t="n">
+        <v>64.22</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>0.498</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>-0.0394</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>571500</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H77" t="n">
+        <v>60.48</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>570200</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H78" t="n">
+        <v>69.61</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>2.019</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>1.976</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>-0.03759999999999999</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>568600</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H79" t="n">
+        <v>40.57</v>
+      </c>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="E80" s="9" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>529800</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H80" t="n">
+        <v>56.08</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>4.494</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="7" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E81" s="9" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>525200</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H81" t="n">
+        <v>50.24</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>1.364</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>1.424</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ANCOMNY</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>517300</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H82" t="n">
+        <v>31.62</v>
+      </c>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0.823</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>-0.04099999999999999</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>516900</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>55.59</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>515700</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H84" t="n">
+        <v>33.47</v>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>1.185</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="E85" s="9" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>510300</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H85" t="n">
+        <v>52.45</v>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="7" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>-0.0184</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>501200</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H86" t="n">
+        <v>43.24</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>1.644</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>1.727</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M54"/>
+  <autoFilter ref="A1:M86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-30/bursa-report-2026-10-30.xlsx
+++ b/docs/downloads/2026-10-30/bursa-report-2026-10-30.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-30" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-30'!$A$1:$M$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-30'!$A$1:$M$134</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M109"/>
+  <dimension ref="A1:M134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.0313</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>15370600</v>
+        <v>17697900</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>66.94</v>
@@ -625,10 +625,10 @@
         <v>-0.1875</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>182500200</v>
+        <v>188029100</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="H3" t="n">
         <v>32.78</v>
@@ -670,10 +670,10 @@
         <v>-0.0667</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>75653200</v>
+        <v>86851900</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="H4" t="n">
         <v>42.73</v>
@@ -709,19 +709,19 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.36</v>
+        <v>0.415</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>-0.3333</v>
+        <v>-0.2315</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>53450900</v>
+        <v>66259800</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>2.17</v>
+        <v>2.69</v>
       </c>
       <c r="H5" t="n">
-        <v>20.67</v>
+        <v>23.34</v>
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.63</v>
+        <v>0.635</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.577</v>
+        <v>0.578</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.29</v>
+        <v>0.305</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>-0.2162</v>
+        <v>-0.1757</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>34244000</v>
+        <v>41082600</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.82</v>
+        <v>0.99</v>
       </c>
       <c r="H6" t="n">
-        <v>33.61</v>
+        <v>35.05</v>
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.416</v>
+        <v>0.417</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>0.345</v>
@@ -805,10 +805,10 @@
         <v>0.0101</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>14692700</v>
+        <v>19977700</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="H7" t="n">
         <v>73.23</v>
@@ -835,28 +835,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.335</v>
+        <v>0.16</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>-0.0147</v>
+        <v>-0.0857</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>11617000</v>
+        <v>12982500</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.16</v>
+        <v>1.36</v>
       </c>
       <c r="H8" t="n">
-        <v>57.95</v>
+        <v>57.77</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.325</v>
+        <v>0.143</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.275</v>
+        <v>0.121</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -880,39 +880,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>-0.0571</v>
+        <v>0.155</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>10926400</v>
+        <v>12930000</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>1.15</v>
+        <v>0.34</v>
       </c>
       <c r="H9" t="n">
-        <v>59.64</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.71</v>
+      </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.144</v>
+        <v>0.156</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.122</v>
+        <v>0.156</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -925,28 +925,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.39</v>
+        <v>0.335</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.0147</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>9562300</v>
+        <v>11893800</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.66</v>
+        <v>0.16</v>
       </c>
       <c r="H10" t="n">
-        <v>35.76</v>
+        <v>57.95</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.446</v>
+        <v>0.325</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.275</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -970,28 +970,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0.0435</v>
+        <v>0.385</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>-0.04940000000000001</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>8915700</v>
+        <v>10833100</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.55</v>
+        <v>0.74</v>
       </c>
       <c r="H11" t="n">
-        <v>73.88</v>
+        <v>35.19</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.105</v>
+        <v>0.445</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,28 +1015,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>-0.0269</v>
+        <v>0.12</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>7753300</v>
+        <v>10630500</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.27</v>
+        <v>1.84</v>
       </c>
       <c r="H12" t="n">
-        <v>61.25</v>
+        <v>73.88</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>2.046</v>
+        <v>0.105</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.851</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,28 +1060,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EWICAP</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>0.0741</v>
+        <v>2.16</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>-0.0314</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>7135300</v>
+        <v>9750400</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>6.02</v>
+        <v>0.34</v>
       </c>
       <c r="H13" t="n">
-        <v>52.26</v>
+        <v>60.52</v>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.138</v>
+        <v>2.045</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.162</v>
+        <v>1.851</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1105,28 +1105,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>EWICAP</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>-0.0343</v>
+        <v>0.14</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>0.03700000000000001</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>6559000</v>
+        <v>7365500</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.89</v>
+        <v>6.21</v>
       </c>
       <c r="H14" t="n">
-        <v>59.45</v>
+        <v>48.52</v>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.87</v>
+        <v>0.137</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.674</v>
+        <v>0.162</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1150,39 +1150,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BINTAI</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>-0.0625</v>
+        <v>0.3</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>6459500</v>
+        <v>7242800</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>3.31</v>
+        <v>0.37</v>
       </c>
       <c r="H15" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.38</v>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.073</v>
+        <v>0.305</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.073</v>
+        <v>0.304</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1195,28 +1195,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0</v>
+        <v>4.72</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>-0.0021</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>6092500</v>
+        <v>7009600</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>1.74</v>
+        <v>0.32</v>
       </c>
       <c r="H16" t="n">
-        <v>49.15</v>
+        <v>47.92</v>
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.295</v>
+        <v>4.728</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.295</v>
+        <v>4.789</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1240,39 +1240,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>0.2</v>
+        <v>0.99</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>-0.0294</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>5506700</v>
+        <v>6971000</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.37</v>
+        <v>0.95</v>
       </c>
       <c r="H17" t="n">
-        <v>59.77</v>
-      </c>
-      <c r="I17" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.79</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.052</v>
+        <v>0.87</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.047</v>
+        <v>0.674</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1285,31 +1285,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>BINTAI</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>0</v>
+        <v>0.075</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>-0.0625</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>5319100</v>
-      </c>
-      <c r="G18" s="12" t="n"/>
-      <c r="I18" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="9" t="n"/>
+        <v>6465000</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="H18" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>0.073</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
     </row>
@@ -1321,28 +1330,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>-0.0333</v>
+        <v>0.775</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>5277300</v>
+        <v>6412400</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="H19" t="n">
-        <v>32.73</v>
+        <v>50.94</v>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
@@ -1350,10 +1359,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.152</v>
+        <v>0.774</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.17</v>
+        <v>0.775</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1366,39 +1375,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>5183900</v>
+        <v>6190000</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="H20" t="n">
-        <v>39.38</v>
-      </c>
-      <c r="I20" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.49</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.305</v>
+        <v>0.867</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.304</v>
+        <v>0.868</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1411,39 +1420,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0070</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>MQTECH</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>4.72</v>
+        <v>0.055</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>-0.0021</v>
+        <v>-0.0833</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>5024500</v>
+        <v>6108000</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.23</v>
+        <v>2.96</v>
       </c>
       <c r="H21" t="n">
-        <v>47.92</v>
-      </c>
-      <c r="I21" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.39</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>4.728</v>
+        <v>0.053</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>4.789</v>
+        <v>0.055</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1456,39 +1465,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.775</v>
+        <v>0.295</v>
       </c>
       <c r="E22" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>4772400</v>
+        <v>6092500</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.31</v>
+        <v>1.74</v>
       </c>
       <c r="H22" t="n">
-        <v>50.94</v>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.15</v>
+      </c>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.774</v>
+        <v>0.295</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.775</v>
+        <v>0.295</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1501,39 +1510,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1.31</v>
+        <v>0.055</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>0.0155</v>
+        <v>0.1</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>4669100</v>
+        <v>6070900</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.68</v>
+        <v>0.41</v>
       </c>
       <c r="H23" t="n">
-        <v>67.29000000000001</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.61</v>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1.213</v>
+        <v>0.051</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>1.164</v>
+        <v>0.047</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1555,19 +1564,19 @@
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="E24" s="16" t="n">
-        <v>0.0242</v>
+        <v>0.0161</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>4356800</v>
+        <v>5933300</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.41</v>
+        <v>0.55</v>
       </c>
       <c r="H24" t="n">
-        <v>70.09</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
@@ -1575,10 +1584,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1.143</v>
+        <v>1.142</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>1.077</v>
+        <v>1.076</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1591,28 +1600,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>1.31</v>
+      </c>
+      <c r="E25" s="16" t="n">
+        <v>0.0155</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>3870800</v>
+        <v>5586300</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.18</v>
+        <v>0.82</v>
       </c>
       <c r="H25" t="n">
-        <v>47.49</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
@@ -1620,10 +1629,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.867</v>
+        <v>1.213</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.868</v>
+        <v>1.164</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1636,40 +1645,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>-0.0333</v>
+        <v>0.005</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>3838900</v>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H26" t="n">
-        <v>52.03</v>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="K26" s="9" t="n">
-        <v>0.554</v>
-      </c>
+        <v>5470100</v>
+      </c>
+      <c r="G26" s="12" t="n"/>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
     </row>
@@ -1681,39 +1681,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0129</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SRIDGE</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>0.0455</v>
+        <v>2.53</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>-0.0269</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>3835800</v>
+        <v>5334000</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>3.42</v>
+        <v>0.32</v>
       </c>
       <c r="H27" t="n">
-        <v>43.81</v>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.91</v>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.118</v>
+        <v>2.589</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.13</v>
+        <v>2.574</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1726,28 +1726,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0126</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>MICROLN</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.38</v>
+        <v>0.075</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>0.0133</v>
+        <v>0.1538</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>3798600</v>
+        <v>5301800</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.34</v>
       </c>
       <c r="H28" t="n">
-        <v>59.17</v>
+        <v>77.38</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.374</v>
+        <v>0.05</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.37</v>
+        <v>0.047</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1771,28 +1771,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>0</v>
+        <v>0.145</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>3739800</v>
+        <v>5299800</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.23</v>
+        <v>0.45</v>
       </c>
       <c r="H29" t="n">
-        <v>53.09</v>
+        <v>32.73</v>
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.819</v>
+        <v>0.152</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1816,33 +1816,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>-0.025</v>
+        <v>6.91</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>0.0029</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>3680000</v>
+        <v>4969600</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.16</v>
+        <v>0.29</v>
+      </c>
+      <c r="H30" t="n">
+        <v>26.59</v>
       </c>
       <c r="I30" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J30" s="9" t="n"/>
-      <c r="K30" s="9" t="n"/>
+      <c r="J30" s="9" t="n">
+        <v>7.239</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>7.566</v>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
     </row>
@@ -1863,19 +1870,19 @@
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>-0.0526</v>
+        <v>-0.0175</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3547800</v>
+        <v>4822800</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="H31" t="n">
-        <v>44.52</v>
+        <v>48.32</v>
       </c>
       <c r="I31" s="15" t="inlineStr">
         <is>
@@ -1883,7 +1890,7 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.282</v>
+        <v>0.283</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>0.279</v>
@@ -1899,36 +1906,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E32" s="16" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.82</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3544200</v>
+        <v>4785800</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="H32" t="n">
-        <v>51.19</v>
-      </c>
-      <c r="I32" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J32" s="9" t="n"/>
-      <c r="K32" s="9" t="n"/>
+        <v>53.09</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
     </row>
@@ -1940,28 +1951,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E33" s="16" t="n">
-        <v>0.0108</v>
+        <v>0.58</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>3525600</v>
+        <v>4749000</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>1.68</v>
+        <v>0.25</v>
       </c>
       <c r="H33" t="n">
-        <v>59.25</v>
+        <v>52.03</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1969,10 +1980,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.463</v>
+        <v>0.576</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.462</v>
+        <v>0.554</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1985,39 +1996,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>2.55</v>
+        <v>0.545</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>-0.0693</v>
+        <v>-0.0091</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>3217800</v>
+        <v>4573100</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>0.96</v>
       </c>
       <c r="H34" t="n">
-        <v>33.94</v>
-      </c>
-      <c r="I34" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.72</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>3.032</v>
+        <v>0.48</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>2.67</v>
+        <v>0.443</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2030,39 +2041,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>-0.0269</v>
+        <v>0.38</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>3104600</v>
+        <v>4547000</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.18</v>
+        <v>0.67</v>
       </c>
       <c r="H35" t="n">
-        <v>45.91</v>
-      </c>
-      <c r="I35" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.17</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>2.589</v>
+        <v>0.374</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>2.574</v>
+        <v>0.37</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2075,40 +2086,33 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>0.0058</v>
+        <v>0.195</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>3061700</v>
+        <v>4092400</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>0.18</v>
       </c>
-      <c r="H36" t="n">
-        <v>28.14</v>
-      </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J36" s="9" t="n">
-        <v>7.241</v>
-      </c>
-      <c r="K36" s="9" t="n">
-        <v>7.567</v>
-      </c>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="9" t="n"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
     </row>
@@ -2120,39 +2124,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>-0.04</v>
+        <v>2.17</v>
+      </c>
+      <c r="E37" s="16" t="n">
+        <v>0.0046</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>2953400</v>
+        <v>3901300</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>1.22</v>
+        <v>0.3</v>
       </c>
       <c r="H37" t="n">
-        <v>39.95</v>
-      </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.25</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.379</v>
+        <v>2.114</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.385</v>
+        <v>2.224</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2165,39 +2169,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0129</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SRIDGE</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>0</v>
+        <v>0.115</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>2902800</v>
+        <v>3876600</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.55</v>
+        <v>3.46</v>
       </c>
       <c r="H38" t="n">
-        <v>39.02</v>
-      </c>
-      <c r="I38" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.81</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.412</v>
+        <v>0.118</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.438</v>
+        <v>0.13</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2210,40 +2214,36 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>0</v>
+        <v>0.225</v>
+      </c>
+      <c r="E39" s="16" t="n">
+        <v>0.04650000000000001</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>2762800</v>
+        <v>3644600</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.29</v>
+        <v>0.19</v>
       </c>
       <c r="H39" t="n">
-        <v>41.22</v>
+        <v>51.19</v>
       </c>
       <c r="I39" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J39" s="9" t="n">
-        <v>2.704</v>
-      </c>
-      <c r="K39" s="9" t="n">
-        <v>2.75</v>
-      </c>
+      <c r="J39" s="9" t="n"/>
+      <c r="K39" s="9" t="n"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
     </row>
@@ -2255,28 +2255,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.415</v>
+        <v>0.47</v>
       </c>
       <c r="E40" s="16" t="n">
-        <v>0.0122</v>
+        <v>0.0108</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2492700</v>
+        <v>3588700</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.21</v>
+        <v>1.71</v>
       </c>
       <c r="H40" t="n">
-        <v>55.59</v>
+        <v>59.25</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.404</v>
+        <v>0.463</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.386</v>
+        <v>0.462</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2300,39 +2300,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.445</v>
+        <v>2.49</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>-0.0111</v>
+        <v>-0.09119999999999999</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>2376200</v>
+        <v>3509300</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="H41" t="n">
-        <v>46.04</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.51</v>
+      </c>
+      <c r="I41" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.452</v>
+        <v>3.026</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.47</v>
+        <v>2.668</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2345,28 +2345,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>2.16</v>
+        <v>0.185</v>
       </c>
       <c r="E42" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>2261900</v>
+        <v>3466900</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="H42" t="n">
-        <v>53.37</v>
+        <v>49.14</v>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>2.114</v>
+        <v>0.185</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>2.224</v>
+        <v>0.187</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2390,39 +2390,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>3.97</v>
+        <v>2.64</v>
       </c>
       <c r="E43" s="16" t="n">
-        <v>0.0258</v>
+        <v>0.0038</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2240700</v>
+        <v>3383200</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>0.35</v>
       </c>
       <c r="H43" t="n">
-        <v>57.13</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.37</v>
+      </c>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>3.856</v>
+        <v>2.705</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>3.42</v>
+        <v>2.75</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2435,28 +2435,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>-0.0182</v>
+        <v>0.645</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>2188700</v>
+        <v>3213500</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
       <c r="H44" t="n">
-        <v>76.89</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.48</v>
+        <v>0.631</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.443</v>
+        <v>0.62</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2480,28 +2480,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.665</v>
+        <v>0.42</v>
       </c>
       <c r="E45" s="16" t="n">
-        <v>0.0153</v>
+        <v>0.0244</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>2127500</v>
+        <v>2994400</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.85</v>
+        <v>0.26</v>
       </c>
       <c r="H45" t="n">
-        <v>64.3</v>
+        <v>57.09</v>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.644</v>
+        <v>0.404</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.633</v>
+        <v>0.386</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2525,28 +2525,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.93</v>
+        <v>0.36</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>-0.0159</v>
+        <v>-0.04</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>2123400</v>
+        <v>2960600</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.18</v>
+        <v>1.22</v>
       </c>
       <c r="H46" t="n">
-        <v>41.3</v>
+        <v>39.95</v>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.982</v>
+        <v>0.379</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.997</v>
+        <v>0.385</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2570,28 +2570,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>-0.0256</v>
+        <v>0.39</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2073800</v>
+        <v>2954800</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.23</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>43.28</v>
+        <v>39.02</v>
       </c>
       <c r="I47" s="15" t="inlineStr">
         <is>
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.601</v>
+        <v>0.412</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.619</v>
+        <v>0.438</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2615,28 +2615,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>-0.014</v>
+        <v>0.84</v>
+      </c>
+      <c r="E48" s="16" t="n">
+        <v>0.012</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2032900</v>
+        <v>2839500</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.11</v>
+        <v>0.57</v>
       </c>
       <c r="H48" t="n">
-        <v>53.08</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>4.904</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>4.804</v>
+        <v>0.785</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2660,28 +2660,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>0</v>
+        <v>0.445</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>-0.0111</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2021300</v>
+        <v>2673400</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="H49" t="n">
-        <v>66.40000000000001</v>
+        <v>46.04</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.631</v>
+        <v>0.452</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.62</v>
+        <v>0.47</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2714,19 +2714,19 @@
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.475</v>
+        <v>0.48</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>-0.0206</v>
+        <v>-0.0103</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1953800</v>
+        <v>2616200</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="H50" t="n">
-        <v>42.66</v>
+        <v>44.16</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.49</v>
+        <v>0.491</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>0.509</v>
@@ -2750,39 +2750,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>2.35</v>
+        <v>3.97</v>
       </c>
       <c r="E51" s="16" t="n">
-        <v>0.0307</v>
+        <v>0.0258</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1944200</v>
+        <v>2473700</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.54</v>
+        <v>0.39</v>
       </c>
       <c r="H51" t="n">
-        <v>55.12</v>
-      </c>
-      <c r="I51" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.13</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>2.301</v>
+        <v>3.856</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>2.231</v>
+        <v>3.42</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2795,39 +2795,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>0</v>
+        <v>0.925</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>-0.0212</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1787300</v>
+        <v>2465600</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>1.42</v>
+        <v>0.21</v>
       </c>
       <c r="H52" t="n">
-        <v>45.53</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.72</v>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.223</v>
+        <v>0.982</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.229</v>
+        <v>0.997</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2840,39 +2840,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E53" s="17" t="n">
-        <v>0</v>
+        <v>4.93</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>-0.014</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1762800</v>
+        <v>2385000</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.82</v>
+        <v>0.13</v>
       </c>
       <c r="H53" t="n">
-        <v>29.78</v>
-      </c>
-      <c r="I53" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.08</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.428</v>
+        <v>4.904</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.45</v>
+        <v>4.804</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2885,39 +2885,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>6.77</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>-0.0131</v>
+        <v>1.16</v>
+      </c>
+      <c r="E54" s="16" t="n">
+        <v>0.0175</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1721000</v>
+        <v>2270700</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="H54" t="n">
-        <v>58.26</v>
-      </c>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.28</v>
+      </c>
+      <c r="I54" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>6.479</v>
+        <v>1.187</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>6.077</v>
+        <v>1.265</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2930,39 +2930,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>0</v>
+        <v>0.9</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>-0.005500000000000001</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1721000</v>
+        <v>2238300</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.23</v>
+        <v>1.12</v>
       </c>
       <c r="H55" t="n">
-        <v>32.68</v>
-      </c>
-      <c r="I55" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.6</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.305</v>
+        <v>0.904</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.35</v>
+        <v>0.899</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2975,28 +2975,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.845</v>
+        <v>0.665</v>
       </c>
       <c r="E56" s="16" t="n">
-        <v>0.0181</v>
+        <v>0.0153</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1709200</v>
+        <v>2190600</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.34</v>
+        <v>0.87</v>
       </c>
       <c r="H56" t="n">
-        <v>73.44</v>
+        <v>64.3</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.644</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.785</v>
+        <v>0.633</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3020,39 +3020,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E57" s="17" t="n">
-        <v>0</v>
+        <v>2.34</v>
+      </c>
+      <c r="E57" s="16" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1673600</v>
+        <v>2163300</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.84</v>
+        <v>0.6</v>
       </c>
       <c r="H57" t="n">
-        <v>50.77</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.49</v>
+      </c>
+      <c r="I57" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.904</v>
+        <v>2.3</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.899</v>
+        <v>2.231</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3065,28 +3065,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.775</v>
+        <v>0.575</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>-0.0127</v>
+        <v>-0.0171</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1641300</v>
+        <v>2156700</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="H58" t="n">
-        <v>51.24</v>
+        <v>44.03</v>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
@@ -3094,10 +3094,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.772</v>
+        <v>0.601</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.771</v>
+        <v>0.619</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3110,28 +3110,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.665</v>
+        <v>6.74</v>
       </c>
       <c r="E59" s="10" t="n">
-        <v>-0.0148</v>
+        <v>-0.0175</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1551700</v>
+        <v>2111600</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.34</v>
+        <v>0.37</v>
       </c>
       <c r="H59" t="n">
-        <v>61.63</v>
+        <v>57.59</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.616</v>
+        <v>6.476</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.589</v>
+        <v>6.076</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3155,39 +3155,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.45</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>-0.0426</v>
+        <v>-0.003</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1508600</v>
+        <v>2080400</v>
       </c>
       <c r="G60" s="12" t="n">
         <v>0.18</v>
       </c>
       <c r="H60" t="n">
-        <v>42.73</v>
-      </c>
-      <c r="I60" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.63</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.483</v>
+        <v>9.992000000000001</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.475</v>
+        <v>10.088</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3200,39 +3200,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>-0.007900000000000001</v>
+        <v>6.31</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>0.0016</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1508400</v>
+        <v>2017500</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="H61" t="n">
-        <v>54.42</v>
-      </c>
-      <c r="I61" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.54</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>1.246</v>
+        <v>6.329</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>1.216</v>
+        <v>6.568</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3245,28 +3245,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.44</v>
+        <v>2.62</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>-0.033</v>
+        <v>-0.0224</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1508200</v>
+        <v>1797400</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
       <c r="H62" t="n">
-        <v>52.81</v>
+        <v>51.14</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.433</v>
+        <v>2.612</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.417</v>
+        <v>2.597</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3290,28 +3290,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>-0.0048</v>
+        <v>1.25</v>
+      </c>
+      <c r="E63" s="16" t="n">
+        <v>0.0246</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1492800</v>
+        <v>1796900</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="H63" t="n">
-        <v>45.25</v>
+        <v>41.68</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>2.102</v>
+        <v>1.273</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>2.116</v>
+        <v>1.459</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3335,39 +3335,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>2.62</v>
+        <v>0.77</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>-0.0224</v>
+        <v>-0.0191</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1419800</v>
+        <v>1787700</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="H64" t="n">
-        <v>51.14</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.61</v>
+      </c>
+      <c r="I64" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>2.612</v>
+        <v>0.771</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>2.597</v>
+        <v>0.771</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3380,28 +3380,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E65" s="16" t="n">
-        <v>0.0152</v>
+        <v>0.22</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1382200</v>
+        <v>1787300</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.88</v>
+        <v>1.42</v>
       </c>
       <c r="H65" t="n">
-        <v>57.2</v>
+        <v>45.53</v>
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.321</v>
+        <v>0.223</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.33</v>
+        <v>0.229</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3425,39 +3425,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>-0.001</v>
+        <v>0.385</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1380300</v>
+        <v>1777000</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.12</v>
+        <v>0.82</v>
       </c>
       <c r="H66" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.17</v>
+      </c>
+      <c r="I66" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>9.994</v>
+        <v>0.428</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>10.088</v>
+        <v>0.45</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3470,28 +3470,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>1.25</v>
+        <v>5.32</v>
       </c>
       <c r="E67" s="16" t="n">
-        <v>0.0246</v>
+        <v>0.0038</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1350400</v>
+        <v>1768700</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="H67" t="n">
-        <v>41.68</v>
+        <v>47.8</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3499,10 +3499,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>1.273</v>
+        <v>5.351</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>1.459</v>
+        <v>5.539</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3515,39 +3515,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>-0.0455</v>
+        <v>0.28</v>
+      </c>
+      <c r="E68" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1314500</v>
+        <v>1763200</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="H68" t="n">
-        <v>57.95</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.68</v>
+      </c>
+      <c r="I68" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.594</v>
+        <v>0.305</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.503</v>
+        <v>0.35</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3560,28 +3560,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>0</v>
+        <v>0.665</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>-0.0148</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1310200</v>
+        <v>1659000</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.09</v>
+        <v>0.36</v>
       </c>
       <c r="H69" t="n">
-        <v>32.88</v>
+        <v>61.63</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.466</v>
+        <v>0.616</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.574</v>
+        <v>0.589</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3605,40 +3605,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SCGM</t>
+          <t>BPROP</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.365</v>
+        <v>0.245</v>
       </c>
       <c r="E70" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1298200</v>
-      </c>
-      <c r="G70" s="12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="H70" t="n">
-        <v>66.39</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J70" s="9" t="n">
-        <v>0.349</v>
-      </c>
-      <c r="K70" s="9" t="n">
-        <v>0.332</v>
-      </c>
+        <v>1631500</v>
+      </c>
+      <c r="G70" s="12" t="n"/>
+      <c r="I70" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="n"/>
+      <c r="K70" s="9" t="n"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
     </row>
@@ -3650,28 +3641,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E71" s="17" t="n">
-        <v>0</v>
+        <v>1.54</v>
+      </c>
+      <c r="E71" s="16" t="n">
+        <v>0.0199</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1280900</v>
+        <v>1623600</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="H71" t="n">
-        <v>44.77</v>
+        <v>43.01</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
@@ -3679,10 +3670,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>6.328</v>
+        <v>1.554</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>6.568</v>
+        <v>1.808</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3695,39 +3686,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="E72" s="16" t="n">
-        <v>0.0038</v>
+        <v>0.865</v>
+      </c>
+      <c r="E72" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1252000</v>
+        <v>1620800</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.08</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H72" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.59</v>
+      </c>
+      <c r="I72" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>5.351</v>
+        <v>0.866</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>5.539</v>
+        <v>0.861</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3740,28 +3731,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E73" s="16" t="n">
-        <v>0.0062</v>
+        <v>0.45</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>-0.0426</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1219000</v>
+        <v>1616600</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.45</v>
+        <v>0.19</v>
       </c>
       <c r="H73" t="n">
-        <v>36.16</v>
+        <v>42.73</v>
       </c>
       <c r="I73" s="15" t="inlineStr">
         <is>
@@ -3769,10 +3760,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.823</v>
+        <v>0.483</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.852</v>
+        <v>0.475</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3785,28 +3776,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>-0.0067</v>
+        <v>0.805</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1210500</v>
+        <v>1589600</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="H74" t="n">
-        <v>50.46</v>
+        <v>31.62</v>
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
@@ -3814,10 +3805,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.745</v>
+        <v>0.823</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.709</v>
+        <v>0.851</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3830,39 +3821,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>-0.0227</v>
+        <v>2.09</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1191100</v>
+        <v>1576500</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="H75" t="n">
-        <v>40.59</v>
-      </c>
-      <c r="I75" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.16</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.221</v>
+        <v>2.103</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.257</v>
+        <v>2.116</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3875,33 +3866,40 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>-0.0276</v>
+        <v>0.44</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1173300</v>
+        <v>1561600</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I76" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J76" s="9" t="n"/>
-      <c r="K76" s="9" t="n"/>
+        <v>0.11</v>
+      </c>
+      <c r="H76" t="n">
+        <v>32.88</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="K76" s="9" t="n">
+        <v>0.574</v>
+      </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
     </row>
@@ -3913,28 +3911,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="E77" s="16" t="n">
-        <v>0.0199</v>
+        <v>0.44</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>-0.033</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1171500</v>
+        <v>1553200</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.08</v>
+        <v>0.22</v>
       </c>
       <c r="H77" t="n">
-        <v>43.01</v>
+        <v>52.81</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3942,10 +3940,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>1.554</v>
+        <v>0.433</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>1.808</v>
+        <v>0.417</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3958,28 +3956,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E78" s="16" t="n">
-        <v>0.0279</v>
+        <v>0.63</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>-0.0455</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1130500</v>
+        <v>1551600</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="H78" t="n">
-        <v>56.93</v>
+        <v>57.95</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -3987,10 +3985,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>2.485</v>
+        <v>0.594</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>2.602</v>
+        <v>0.503</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4003,28 +4001,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.58</v>
+        <v>1.26</v>
       </c>
       <c r="E79" s="10" t="n">
-        <v>-0.0413</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1090300</v>
+        <v>1511500</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.14</v>
+        <v>0.24</v>
       </c>
       <c r="H79" t="n">
-        <v>36.36</v>
+        <v>54.42</v>
       </c>
       <c r="I79" s="15" t="inlineStr">
         <is>
@@ -4032,10 +4030,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.631</v>
+        <v>1.246</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.673</v>
+        <v>1.216</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4048,28 +4046,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E80" s="17" t="n">
-        <v>0</v>
+        <v>0.34</v>
+      </c>
+      <c r="E80" s="16" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1070100</v>
+        <v>1388000</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.14</v>
+        <v>0.89</v>
       </c>
       <c r="H80" t="n">
-        <v>40.03</v>
+        <v>59.3</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4077,10 +4075,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.266</v>
+        <v>0.322</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.287</v>
+        <v>0.33</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4108,10 +4106,10 @@
         <v>0.0141</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1016100</v>
+        <v>1314900</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>2.74</v>
+        <v>3.54</v>
       </c>
       <c r="H81" t="n">
         <v>73.81</v>
@@ -4138,28 +4136,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>-0.0083</v>
+        <v>1.39</v>
+      </c>
+      <c r="E82" s="16" t="n">
+        <v>0.0221</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>970600</v>
+        <v>1307700</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.65</v>
+        <v>0.51</v>
       </c>
       <c r="H82" t="n">
-        <v>64.72</v>
+        <v>51.65</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -4167,10 +4165,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>2.183</v>
+        <v>1.365</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>2.219</v>
+        <v>1.424</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4183,28 +4181,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E83" s="16" t="n">
-        <v>0.0221</v>
+        <v>2.88</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>946100</v>
+        <v>1307100</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="H83" t="n">
-        <v>51.65</v>
+        <v>45.7</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4212,10 +4210,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>1.365</v>
+        <v>2.991</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.424</v>
+        <v>2.883</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4228,28 +4226,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CITAGLB</t>
+          <t>SCGM</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E84" s="16" t="n">
-        <v>0.06309999999999999</v>
+        <v>0.365</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>935700</v>
+        <v>1298200</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>3.74</v>
+        <v>1.66</v>
       </c>
       <c r="H84" t="n">
-        <v>68.92</v>
+        <v>66.39</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -4257,10 +4255,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>1.065</v>
+        <v>0.349</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>1.051</v>
+        <v>0.332</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4273,28 +4271,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1.3</v>
+        <v>0.74</v>
       </c>
       <c r="E85" s="10" t="n">
-        <v>-0.0299</v>
+        <v>-0.0067</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>875700</v>
+        <v>1275500</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="H85" t="n">
-        <v>52.98</v>
+        <v>50.46</v>
       </c>
       <c r="I85" s="15" t="inlineStr">
         <is>
@@ -4302,10 +4300,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>1.289</v>
+        <v>0.745</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1.199</v>
+        <v>0.709</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4318,39 +4316,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="E86" s="16" t="n">
-        <v>0.0053</v>
+        <v>0.25</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>850600</v>
+        <v>1275400</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="H86" t="n">
-        <v>58.45</v>
-      </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.78</v>
+      </c>
+      <c r="I86" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.908</v>
+        <v>0.261</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.952</v>
+        <v>0.276</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4363,40 +4361,33 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>1.59</v>
+        <v>0.71</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>-0.0245</v>
+        <v>-0.0207</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>838900</v>
+        <v>1261300</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H87" t="n">
-        <v>42.39</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J87" s="9" t="n">
-        <v>1.643</v>
-      </c>
-      <c r="K87" s="9" t="n">
-        <v>1.727</v>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="I87" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="n"/>
+      <c r="K87" s="9" t="n"/>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
     </row>
@@ -4408,28 +4399,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="E88" s="16" t="n">
-        <v>0.008800000000000001</v>
+        <v>4.2</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>837800</v>
+        <v>1255000</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="H88" t="n">
-        <v>55.41</v>
+        <v>59.06</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -4437,10 +4428,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>4.492</v>
+        <v>4.057</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>4.449</v>
+        <v>3.728</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4453,28 +4444,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>-0.0204</v>
+        <v>2.16</v>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>0.009300000000000001</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>828300</v>
+        <v>1231700</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="H89" t="n">
-        <v>45.7</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -4482,10 +4473,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>2.991</v>
+        <v>2.021</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>2.883</v>
+        <v>1.977</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4498,39 +4489,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.755</v>
+        <v>1.29</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>-0.0258</v>
+        <v>-0.0373</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>806400</v>
+        <v>1225400</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.15</v>
+        <v>0.44</v>
       </c>
       <c r="H90" t="n">
-        <v>52.71</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.98</v>
+      </c>
+      <c r="I90" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.75</v>
+        <v>1.289</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.702</v>
+        <v>1.199</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4543,28 +4534,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>-0.0313</v>
+        <v>2.58</v>
+      </c>
+      <c r="E91" s="16" t="n">
+        <v>0.0279</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>794100</v>
+        <v>1220100</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="H91" t="n">
-        <v>64.22</v>
+        <v>56.93</v>
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
@@ -4572,10 +4563,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>2.485</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.498</v>
+        <v>2.602</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4588,39 +4579,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>3.88</v>
+        <v>0.215</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>-0.0177</v>
+        <v>-0.0227</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>794000</v>
+        <v>1194400</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="H92" t="n">
-        <v>52.41</v>
-      </c>
-      <c r="I92" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.59</v>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>3.852</v>
+        <v>0.221</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>3.785</v>
+        <v>0.257</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4633,39 +4624,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="E93" s="16" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.58</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>-0.0413</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>777400</v>
+        <v>1141100</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="H93" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="I93" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.36</v>
+      </c>
+      <c r="I93" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>2.02</v>
+        <v>0.631</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1.976</v>
+        <v>0.673</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4678,28 +4669,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E94" s="10" t="n">
-        <v>-0.0236</v>
+        <v>0.265</v>
+      </c>
+      <c r="E94" s="16" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>746500</v>
+        <v>1105300</v>
       </c>
       <c r="G94" s="12" t="n">
         <v>0.14</v>
       </c>
       <c r="H94" t="n">
-        <v>62.76</v>
+        <v>44.9</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -4707,10 +4698,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.149</v>
+        <v>0.267</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1.01</v>
+        <v>0.287</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4723,39 +4714,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E95" s="17" t="n">
-        <v>0</v>
+        <v>1.6</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>-0.0184</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>635700</v>
+        <v>1073500</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="H95" t="n">
-        <v>33.47</v>
-      </c>
-      <c r="I95" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.24</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>1.185</v>
+        <v>1.644</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>1.265</v>
+        <v>1.727</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4768,28 +4759,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.58</v>
+        <v>2.38</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>-0.0492</v>
+        <v>-0.0083</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>630500</v>
+        <v>1072700</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.13</v>
+        <v>0.72</v>
       </c>
       <c r="H96" t="n">
-        <v>54.55</v>
+        <v>64.72</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -4797,10 +4788,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.5639999999999999</v>
+        <v>2.183</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.535</v>
+        <v>2.219</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4813,28 +4804,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>-0.02</v>
+        <v>0.95</v>
+      </c>
+      <c r="E97" s="16" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>629600</v>
+        <v>1041700</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.11</v>
+        <v>0.23</v>
       </c>
       <c r="H97" t="n">
-        <v>40.34</v>
+        <v>59.55</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -4842,10 +4833,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>2.603</v>
+        <v>0.909</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>2.798</v>
+        <v>0.952</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4858,28 +4849,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E98" s="17" t="n">
-        <v>0</v>
+        <v>3.88</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>-0.0177</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>623600</v>
+        <v>968600</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.43</v>
+        <v>0.26</v>
       </c>
       <c r="H98" t="n">
-        <v>60.22</v>
+        <v>52.41</v>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
@@ -4887,10 +4878,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>0.619</v>
+        <v>3.852</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0.554</v>
+        <v>3.785</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4903,28 +4894,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PANTECH</t>
+          <t>CITAGLB</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E99" s="17" t="n">
-        <v>0</v>
+        <v>1.16</v>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>0.045</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>615400</v>
+        <v>935800</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>1.42</v>
+        <v>3.75</v>
       </c>
       <c r="H99" t="n">
-        <v>68.33</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -4932,10 +4923,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.665</v>
+        <v>1.064</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.662</v>
+        <v>1.051</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4948,39 +4939,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>-0.03759999999999999</v>
+        <v>4.61</v>
+      </c>
+      <c r="E100" s="16" t="n">
+        <v>0.008800000000000001</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>613700</v>
+        <v>932500</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="H100" t="n">
-        <v>40.57</v>
-      </c>
-      <c r="I100" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.41</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.697</v>
+        <v>4.492</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.6919999999999999</v>
+        <v>4.449</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4993,28 +4984,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="E101" s="17" t="n">
-        <v>0</v>
+        <v>1.22</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>-0.0394</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>613700</v>
+        <v>921000</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
       <c r="H101" t="n">
-        <v>57.21</v>
+        <v>60.48</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -5022,10 +5013,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>1.64</v>
+        <v>1.147</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>1.665</v>
+        <v>1.009</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5038,28 +5029,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>4.19</v>
+        <v>0.75</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>-0.0071</v>
+        <v>-0.0323</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>607900</v>
+        <v>911900</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="H102" t="n">
-        <v>58.57</v>
+        <v>51.76</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -5067,10 +5058,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>4.056</v>
+        <v>0.75</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>3.728</v>
+        <v>0.702</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5083,39 +5074,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>1.27</v>
+        <v>0.83</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>-0.0155</v>
+        <v>-0.0119</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>600500</v>
+        <v>849000</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="H103" t="n">
-        <v>50.45</v>
-      </c>
-      <c r="I103" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.07</v>
+      </c>
+      <c r="I103" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>1.269</v>
+        <v>0.857</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>1.27</v>
+        <v>0.913</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5128,39 +5119,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E104" s="17" t="n">
-        <v>0</v>
+        <v>0.62</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>577000</v>
+        <v>837700</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="H104" t="n">
-        <v>49.59</v>
-      </c>
-      <c r="I104" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.22</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.866</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.861</v>
+        <v>0.498</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5173,39 +5164,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.83</v>
+        <v>0.645</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>-0.0235</v>
+        <v>-0.0301</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>562000</v>
+        <v>807500</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="H105" t="n">
-        <v>42.55</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.17</v>
+      </c>
+      <c r="I105" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.874</v>
+        <v>0.698</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.87</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5218,28 +5209,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>-0.005600000000000001</v>
+        <v>6.89</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>0.0044</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>556800</v>
+        <v>789200</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.38</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H106" t="n">
-        <v>36.93</v>
+        <v>42.63</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -5247,10 +5238,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.914</v>
+        <v>6.98</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.971</v>
+        <v>7.415</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5263,28 +5254,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>0336</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>WINSTAR</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E107" s="10" t="n">
-        <v>-0.027</v>
+        <v>0.64</v>
+      </c>
+      <c r="E107" s="16" t="n">
+        <v>0.024</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>556500</v>
+        <v>782500</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.78</v>
+        <v>1.57</v>
       </c>
       <c r="H107" t="n">
-        <v>44.15</v>
+        <v>55.55</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -5292,10 +5283,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>1.465</v>
+        <v>0.635</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>1.569</v>
+        <v>0.648</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5308,28 +5299,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="E108" s="17" t="n">
-        <v>0</v>
+        <v>0.825</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>-0.0294</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>543900</v>
+        <v>763200</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.05</v>
+        <v>0.13</v>
       </c>
       <c r="H108" t="n">
-        <v>41.27</v>
+        <v>41.94</v>
       </c>
       <c r="I108" s="13" t="inlineStr">
         <is>
@@ -5337,10 +5328,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>6.977</v>
+        <v>0.874</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>7.414</v>
+        <v>0.87</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5353,45 +5344,1170 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>3.89</v>
+        <v>0.59</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>-0.0604</v>
+        <v>-0.0328</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>524600</v>
+        <v>752300</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>3.86</v>
+        <v>0.15</v>
       </c>
       <c r="H109" t="n">
-        <v>29.35</v>
-      </c>
-      <c r="I109" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.67</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>4.174</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>4.334</v>
+        <v>0.535</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>746400</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H110" t="n">
+        <v>51.27</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>7.359</v>
+      </c>
+      <c r="K110" s="9" t="n">
+        <v>7.01</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="14" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="E111" s="10" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>740000</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H111" t="n">
+        <v>40.71</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>2.604</v>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>2.799</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="14" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>736600</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H112" t="n">
+        <v>53.42</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>AXIATA</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>-0.0059</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>689000</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H113" t="n">
+        <v>55.61</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>1.639</v>
+      </c>
+      <c r="K113" s="9" t="n">
+        <v>1.665</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="14" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>-0.0259</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>674000</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H114" t="n">
+        <v>54.62</v>
+      </c>
+      <c r="I114" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="14" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>5125</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>PANTECH</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E115" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>664400</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H115" t="n">
+        <v>68.33</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="K115" s="9" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="14" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="E116" s="16" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>646600</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H116" t="n">
+        <v>50.57</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>7.417</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>7.734</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>PGLOBAL</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>625200</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H117" t="n">
+        <v>60.22</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="14" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>-0.0216</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>622500</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H118" t="n">
+        <v>37.77</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="K118" s="9" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="14" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>0056</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>NCT</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>-0.009000000000000001</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>608000</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H119" t="n">
+        <v>42.68</v>
+      </c>
+      <c r="I119" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="K119" s="9" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="14" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>-0.009899999999999999</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>602800</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="H120" t="n">
+        <v>45.82</v>
+      </c>
+      <c r="I120" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K120" s="9" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="14" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>5337</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ECOSHOP</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>596900</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H121" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="I121" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="n">
+        <v>1.395</v>
+      </c>
+      <c r="K121" s="9" t="n">
+        <v>1.444</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="14" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5123</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SENTRAL</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>579400</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H122" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="I122" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="14" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E123" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>576000</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H123" t="n">
+        <v>58.13</v>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="14" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>4162</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>-0.0604</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>573900</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="H124" t="n">
+        <v>29.35</v>
+      </c>
+      <c r="I124" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="n">
+        <v>4.174</v>
+      </c>
+      <c r="K124" s="9" t="n">
+        <v>4.334</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="14" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>BMGREEN</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>560700</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H125" t="n">
+        <v>44.15</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>1.465</v>
+      </c>
+      <c r="K125" s="9" t="n">
+        <v>1.569</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="14" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>-0.005600000000000001</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>556800</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H126" t="n">
+        <v>36.93</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="K126" s="9" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>-0.0255</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>550100</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H127" t="n">
+        <v>55.53</v>
+      </c>
+      <c r="I127" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="n">
+        <v>5.596</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>5.408</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="14" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>549100</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H128" t="n">
+        <v>50.64</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="n">
+        <v>1.254</v>
+      </c>
+      <c r="K128" s="9" t="n">
+        <v>1.142</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="14" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>5335</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>HI</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E129" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>537600</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H129" t="n">
+        <v>32.37</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="n">
+        <v>1.672</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>1.752</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="14" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E130" s="10" t="n">
+        <v>-0.0221</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>527400</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H130" t="n">
+        <v>54.19</v>
+      </c>
+      <c r="I130" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K130" s="9" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>522800</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H131" t="n">
+        <v>56.36</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>10.621</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>9.999000000000001</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="14" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E132" s="16" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>513500</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H132" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="I132" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="K132" s="9" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="14" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>-0.0538</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>511200</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H133" t="n">
+        <v>42.54</v>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>1.291</v>
+      </c>
+      <c r="K133" s="9" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="14" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E134" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>508600</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H134" t="n">
+        <v>45.91</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="K134" s="9" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M109"/>
+  <autoFilter ref="A1:M134"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-30/bursa-report-2026-10-30.xlsx
+++ b/docs/downloads/2026-10-30/bursa-report-2026-10-30.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-30" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-30'!$A$1:$M$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-30'!$A$1:$M$154</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M134"/>
+  <dimension ref="A1:M154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -557,95 +557,103 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>1304400</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>72.31999999999999</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.759</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号出现，但RSI 72.32已进入超买区，现价0.83高于50日均线0.683约21.5%，短期涨幅偏大，信号可靠性需谨慎看待。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>7106</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>SUPERMX</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0.0313</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>17697900</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>66.94</v>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0.451</v>
-      </c>
-      <c r="K2" s="3" t="n">
+      <c r="D3" s="3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.0208</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>19096100</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>65.97</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K3" s="3" t="n">
         <v>0.402</v>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>🎯 SAR 转多</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr">
-        <is>
-          <t>SAR转多信号，现价0.495高于50日均线0.402，RSI 66.94接近超买区，信号可靠性中等偏强。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ZETRIX</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>-0.1875</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>188029100</v>
-      </c>
-      <c r="G3" s="12" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="H3" t="n">
-        <v>32.78</v>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>0.211</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="14" t="inlineStr"/>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，现价0.49高于50日均线0.402，RSI 65.97接近超买区，信号可靠性中等偏强。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -655,39 +663,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.14</v>
+        <v>0.065</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>-0.0667</v>
+        <v>-0.1875</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>86851900</v>
+        <v>196684100</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>1.8</v>
+        <v>0.54</v>
       </c>
       <c r="H4" t="n">
-        <v>42.73</v>
-      </c>
-      <c r="I4" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>32.78</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.157</v>
+        <v>0.092</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.15</v>
+        <v>0.211</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -700,28 +708,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.415</v>
+        <v>0.145</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>-0.2315</v>
+        <v>-0.0333</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>66259800</v>
+        <v>87764200</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>2.69</v>
+        <v>1.82</v>
       </c>
       <c r="H5" t="n">
-        <v>23.34</v>
+        <v>44.67</v>
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
@@ -729,10 +737,10 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.635</v>
+        <v>0.157</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.578</v>
+        <v>0.15</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -745,28 +753,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.305</v>
+        <v>0.36</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>-0.1757</v>
+        <v>-0.3333</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>41082600</v>
+        <v>72617700</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.99</v>
+        <v>2.95</v>
       </c>
       <c r="H6" t="n">
-        <v>35.05</v>
+        <v>20.67</v>
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
@@ -774,10 +782,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.417</v>
+        <v>0.63</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.345</v>
+        <v>0.577</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -790,39 +798,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>0.0101</v>
+        <v>0.28</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>-0.2432</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>19977700</v>
+        <v>44035000</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.25</v>
+        <v>1.06</v>
       </c>
       <c r="H7" t="n">
-        <v>73.23</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.71</v>
+      </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.901</v>
+        <v>0.415</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.789</v>
+        <v>0.344</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -835,28 +843,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.16</v>
+        <v>0.335</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>-0.0857</v>
+        <v>-0.0147</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>12982500</v>
+        <v>30337700</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>1.36</v>
+        <v>0.41</v>
       </c>
       <c r="H8" t="n">
-        <v>57.77</v>
+        <v>57.95</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -864,10 +872,10 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.143</v>
+        <v>0.325</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.121</v>
+        <v>0.275</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -880,39 +888,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>0</v>
+        <v>0.995</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>0.0051</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>12930000</v>
+        <v>23804000</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="H9" t="n">
-        <v>47.71</v>
-      </c>
-      <c r="I9" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.76000000000001</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.156</v>
+        <v>0.9</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.156</v>
+        <v>0.789</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -925,39 +933,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>-0.0147</v>
+        <v>0.155</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>11893800</v>
+        <v>22828000</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.16</v>
+        <v>0.61</v>
       </c>
       <c r="H10" t="n">
-        <v>57.95</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.71</v>
+      </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.325</v>
+        <v>0.156</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.275</v>
+        <v>0.156</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -970,28 +978,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.385</v>
+        <v>0.16</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>-0.04940000000000001</v>
+        <v>-0.0857</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>10833100</v>
+        <v>13552500</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.74</v>
+        <v>1.42</v>
       </c>
       <c r="H11" t="n">
-        <v>35.19</v>
+        <v>57.77</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
@@ -999,10 +1007,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.445</v>
+        <v>0.143</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.121</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,28 +1023,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>0.0435</v>
+        <v>0.385</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>-0.04940000000000001</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>10630500</v>
+        <v>11165500</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1.84</v>
+        <v>0.77</v>
       </c>
       <c r="H12" t="n">
-        <v>73.88</v>
+        <v>35.19</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1044,10 +1052,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.105</v>
+        <v>0.445</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,28 +1068,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>-0.0314</v>
+        <v>0.12</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>9750400</v>
+        <v>11079600</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.34</v>
+        <v>1.92</v>
       </c>
       <c r="H13" t="n">
-        <v>60.52</v>
+        <v>73.88</v>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
@@ -1089,10 +1097,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>2.045</v>
+        <v>0.105</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>1.851</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1105,28 +1113,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EWICAP</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>0.03700000000000001</v>
+        <v>2.15</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>-0.0359</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>7365500</v>
+        <v>10666000</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>6.21</v>
+        <v>0.37</v>
       </c>
       <c r="H14" t="n">
-        <v>48.52</v>
+        <v>59.8</v>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
@@ -1134,10 +1142,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.137</v>
+        <v>2.044</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.162</v>
+        <v>1.851</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1150,39 +1158,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.3</v>
+        <v>0.775</v>
       </c>
       <c r="E15" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>7242800</v>
+        <v>9251000</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.37</v>
+        <v>0.6</v>
       </c>
       <c r="H15" t="n">
-        <v>39.38</v>
-      </c>
-      <c r="I15" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.94</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.305</v>
+        <v>0.774</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.304</v>
+        <v>0.775</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1195,39 +1203,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>-0.0021</v>
+        <v>0.87</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>7009600</v>
+        <v>8685800</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
       <c r="H16" t="n">
-        <v>47.92</v>
-      </c>
-      <c r="I16" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.55</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>4.728</v>
+        <v>0.868</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>4.789</v>
+        <v>0.868</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1240,39 +1248,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>-0.0294</v>
+        <v>4.73</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6971000</v>
+        <v>8189400</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.95</v>
+        <v>0.38</v>
       </c>
       <c r="H17" t="n">
-        <v>59.79</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.94</v>
+      </c>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.87</v>
+        <v>4.729</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.674</v>
+        <v>4.789</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1285,39 +1293,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BINTAI</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>-0.0625</v>
+        <v>0.3</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>6465000</v>
+        <v>8050800</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>3.31</v>
+        <v>0.41</v>
       </c>
       <c r="H18" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.38</v>
+      </c>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.073</v>
+        <v>0.305</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.073</v>
+        <v>0.304</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1330,28 +1338,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>EWICAP</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>0</v>
+        <v>0.14</v>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>0.03700000000000001</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>6412400</v>
+        <v>7367400</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.42</v>
+        <v>6.22</v>
       </c>
       <c r="H19" t="n">
-        <v>50.94</v>
+        <v>48.52</v>
       </c>
       <c r="I19" s="13" t="inlineStr">
         <is>
@@ -1359,10 +1367,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.774</v>
+        <v>0.137</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.775</v>
+        <v>0.162</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1375,28 +1383,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.865</v>
+        <v>0.98</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0392</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>6190000</v>
+        <v>7007400</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.29</v>
+        <v>0.96</v>
       </c>
       <c r="H20" t="n">
-        <v>47.49</v>
+        <v>59.12</v>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
@@ -1404,10 +1412,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.867</v>
+        <v>0.869</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.868</v>
+        <v>0.674</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1420,28 +1428,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0070</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MQTECH</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>-0.0833</v>
+        <v>1.26</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>0.0161</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>6108000</v>
+        <v>6955700</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>2.96</v>
+        <v>0.65</v>
       </c>
       <c r="H21" t="n">
-        <v>52.39</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -1449,10 +1457,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.053</v>
+        <v>1.142</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.055</v>
+        <v>1.076</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1465,39 +1473,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>0</v>
+        <v>1.31</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>0.0155</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>6092500</v>
+        <v>6527000</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1.74</v>
+        <v>0.96</v>
       </c>
       <c r="H22" t="n">
-        <v>49.15</v>
-      </c>
-      <c r="I22" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.29000000000001</v>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.295</v>
+        <v>1.213</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.295</v>
+        <v>1.164</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1510,39 +1518,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>BINTAI</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>0.1</v>
+        <v>0.075</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>-0.0625</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>6070900</v>
+        <v>6515000</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.41</v>
+        <v>3.34</v>
       </c>
       <c r="H23" t="n">
-        <v>55.61</v>
-      </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.8</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.051</v>
+        <v>0.073</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.047</v>
+        <v>0.073</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1555,39 +1563,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>0.0161</v>
+        <v>2.52</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>-0.0308</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>5933300</v>
+        <v>6426100</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.55</v>
+        <v>0.38</v>
       </c>
       <c r="H24" t="n">
-        <v>69.29000000000001</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.32</v>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1.142</v>
+        <v>2.588</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>1.076</v>
+        <v>2.574</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1600,28 +1608,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0070</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>MQTECH</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>0.0155</v>
+        <v>0.05</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>-0.1667</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>5586300</v>
+        <v>6276000</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.82</v>
+        <v>3.04</v>
       </c>
       <c r="H25" t="n">
-        <v>67.29000000000001</v>
+        <v>44.7</v>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
@@ -1629,10 +1637,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1.213</v>
+        <v>0.053</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>1.164</v>
+        <v>0.055</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1645,31 +1653,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0041</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AIMAX</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.005</v>
+        <v>0.04</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>5470100</v>
-      </c>
-      <c r="G26" s="12" t="n"/>
+        <v>6121700</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H26" t="n">
+        <v>27.36</v>
+      </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="n"/>
-      <c r="K26" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>0.067</v>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
     </row>
@@ -1681,28 +1698,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>-0.0269</v>
+        <v>0.295</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>5334000</v>
+        <v>6092500</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.32</v>
+        <v>1.74</v>
       </c>
       <c r="H27" t="n">
-        <v>45.91</v>
+        <v>49.15</v>
       </c>
       <c r="I27" s="15" t="inlineStr">
         <is>
@@ -1710,10 +1727,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>2.589</v>
+        <v>0.295</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>2.574</v>
+        <v>0.295</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1726,36 +1743,36 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0126</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MICROLN</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.075</v>
+        <v>0.055</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>0.1538</v>
+        <v>0.1</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>5301800</v>
+        <v>6070900</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2.34</v>
+        <v>0.41</v>
       </c>
       <c r="H28" t="n">
-        <v>77.38</v>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.61</v>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.05</v>
+        <v>0.051</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0.047</v>
@@ -1771,39 +1788,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>-0.0333</v>
+        <v>6.91</v>
+      </c>
+      <c r="E29" s="16" t="n">
+        <v>0.0029</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>5299800</v>
+        <v>5780500</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.45</v>
+        <v>0.33</v>
       </c>
       <c r="H29" t="n">
-        <v>32.73</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.59</v>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.152</v>
+        <v>7.239</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.17</v>
+        <v>7.566</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1816,39 +1833,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>6.91</v>
+        <v>6.31</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>0.0029</v>
+        <v>0.0016</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4969600</v>
+        <v>5617400</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.29</v>
+        <v>0.72</v>
       </c>
       <c r="H30" t="n">
-        <v>26.59</v>
-      </c>
-      <c r="I30" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.54</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>7.239</v>
+        <v>6.329</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>7.566</v>
+        <v>6.568</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1861,40 +1878,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0041</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>AIMAX</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>-0.0175</v>
+        <v>0.005</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>4822800</v>
-      </c>
-      <c r="G31" s="12" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="H31" t="n">
-        <v>48.32</v>
-      </c>
+        <v>5470100</v>
+      </c>
+      <c r="G31" s="12" t="n"/>
       <c r="I31" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="K31" s="9" t="n">
-        <v>0.279</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="n"/>
+      <c r="K31" s="9" t="n"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
     </row>
@@ -1906,28 +1914,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E32" s="17" t="n">
-        <v>0</v>
+        <v>0.145</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>4785800</v>
+        <v>5454400</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.3</v>
+        <v>0.46</v>
       </c>
       <c r="H32" t="n">
-        <v>53.09</v>
+        <v>32.73</v>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
@@ -1935,10 +1943,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.819</v>
+        <v>0.152</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1966,10 +1974,10 @@
         <v>-0.0333</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>4749000</v>
+        <v>5338400</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="H33" t="n">
         <v>52.03</v>
@@ -1996,28 +2004,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>-0.0091</v>
+        <v>0.82</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>4573100</v>
+        <v>5332000</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.96</v>
+        <v>0.33</v>
       </c>
       <c r="H34" t="n">
-        <v>79.72</v>
+        <v>53.09</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
@@ -2025,10 +2033,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.48</v>
+        <v>0.819</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.443</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2041,28 +2049,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0126</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>MICROLN</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.38</v>
+        <v>0.075</v>
       </c>
       <c r="E35" s="16" t="n">
-        <v>0.0133</v>
+        <v>0.1538</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>4547000</v>
+        <v>5324800</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.67</v>
+        <v>2.35</v>
       </c>
       <c r="H35" t="n">
-        <v>59.17</v>
+        <v>77.38</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2070,10 +2078,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.374</v>
+        <v>0.05</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.37</v>
+        <v>0.047</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2086,33 +2094,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.195</v>
+        <v>0.28</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>-0.025</v>
+        <v>-0.0175</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>4092400</v>
+        <v>5181300</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.18</v>
+        <v>0.44</v>
+      </c>
+      <c r="H36" t="n">
+        <v>48.32</v>
       </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J36" s="9" t="n"/>
-      <c r="K36" s="9" t="n"/>
+      <c r="J36" s="9" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>0.279</v>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
     </row>
@@ -2124,28 +2139,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>2.17</v>
+        <v>0.47</v>
       </c>
       <c r="E37" s="16" t="n">
-        <v>0.0046</v>
+        <v>0.0108</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>3901300</v>
+        <v>4959200</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.3</v>
+        <v>2.36</v>
       </c>
       <c r="H37" t="n">
-        <v>54.25</v>
+        <v>59.25</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
@@ -2153,10 +2168,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>2.114</v>
+        <v>0.463</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>2.224</v>
+        <v>0.462</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2169,40 +2184,36 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0129</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SRIDGE</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.115</v>
+        <v>0.23</v>
       </c>
       <c r="E38" s="16" t="n">
-        <v>0.0455</v>
+        <v>0.0698</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3876600</v>
+        <v>4791900</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>3.46</v>
+        <v>0.26</v>
       </c>
       <c r="H38" t="n">
-        <v>43.81</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J38" s="9" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="K38" s="9" t="n">
-        <v>0.13</v>
-      </c>
+        <v>53.69</v>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="n"/>
+      <c r="K38" s="9" t="n"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
     </row>
@@ -2214,36 +2225,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.225</v>
+        <v>0.38</v>
       </c>
       <c r="E39" s="16" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.0133</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>3644600</v>
+        <v>4662000</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.19</v>
+        <v>0.68</v>
       </c>
       <c r="H39" t="n">
-        <v>51.19</v>
-      </c>
-      <c r="I39" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J39" s="9" t="n"/>
-      <c r="K39" s="9" t="n"/>
+        <v>59.17</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>0.37</v>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
     </row>
@@ -2255,28 +2270,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>0.0108</v>
+        <v>0.545</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>-0.0091</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>3588700</v>
+        <v>4608100</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>1.71</v>
+        <v>0.97</v>
       </c>
       <c r="H40" t="n">
-        <v>59.25</v>
+        <v>79.72</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2284,10 +2299,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.463</v>
+        <v>0.48</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.462</v>
+        <v>0.443</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2300,39 +2315,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>-0.09119999999999999</v>
+        <v>0.645</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>3509300</v>
+        <v>4581400</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>1.05</v>
+        <v>0.45</v>
       </c>
       <c r="H41" t="n">
-        <v>32.51</v>
-      </c>
-      <c r="I41" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.40000000000001</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>3.026</v>
+        <v>0.631</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>2.668</v>
+        <v>0.62</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2345,28 +2360,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>0</v>
+        <v>2.17</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>0.0046</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>3466900</v>
+        <v>4363200</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.19</v>
+        <v>0.34</v>
       </c>
       <c r="H42" t="n">
-        <v>49.14</v>
+        <v>54.25</v>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
@@ -2374,10 +2389,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.185</v>
+        <v>2.114</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.187</v>
+        <v>2.224</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2390,40 +2405,33 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>0.0038</v>
+        <v>0.195</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3383200</v>
+        <v>4092500</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H43" t="n">
-        <v>42.37</v>
+        <v>0.18</v>
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J43" s="9" t="n">
-        <v>2.705</v>
-      </c>
-      <c r="K43" s="9" t="n">
-        <v>2.75</v>
-      </c>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="9" t="n"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
     </row>
@@ -2435,28 +2443,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0129</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SRIDGE</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>0</v>
+        <v>0.115</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>0.0455</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>3213500</v>
+        <v>4075400</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.32</v>
+        <v>3.63</v>
       </c>
       <c r="H44" t="n">
-        <v>66.40000000000001</v>
+        <v>43.81</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
@@ -2464,10 +2472,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.631</v>
+        <v>0.118</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.62</v>
+        <v>0.13</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2480,39 +2488,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E45" s="16" t="n">
-        <v>0.0244</v>
+        <v>2.35</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>-0.1423</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>2994400</v>
+        <v>3806500</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.26</v>
+        <v>1.14</v>
       </c>
       <c r="H45" t="n">
-        <v>57.09</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.61</v>
+      </c>
+      <c r="I45" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.404</v>
+        <v>3.013</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.386</v>
+        <v>2.666</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2525,39 +2533,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>-0.04</v>
+        <v>0.835</v>
+      </c>
+      <c r="E46" s="16" t="n">
+        <v>0.006</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>2960600</v>
+        <v>3796500</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>1.22</v>
+        <v>0.76</v>
       </c>
       <c r="H46" t="n">
-        <v>39.95</v>
-      </c>
-      <c r="I46" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.81</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.379</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.385</v>
+        <v>0.785</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2570,39 +2578,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E47" s="17" t="n">
-        <v>0</v>
+        <v>0.415</v>
+      </c>
+      <c r="E47" s="16" t="n">
+        <v>0.0122</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2954800</v>
+        <v>3774500</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="H47" t="n">
-        <v>39.02</v>
-      </c>
-      <c r="I47" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.59</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.412</v>
+        <v>0.404</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.438</v>
+        <v>0.386</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2615,28 +2623,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>0.012</v>
+        <v>4.93</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>-0.014</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2839500</v>
+        <v>3662000</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.57</v>
+        <v>0.2</v>
       </c>
       <c r="H48" t="n">
-        <v>71.73999999999999</v>
+        <v>53.08</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2644,10 +2652,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>4.904</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.785</v>
+        <v>4.804</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2660,39 +2668,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>-0.0111</v>
+        <v>2.64</v>
+      </c>
+      <c r="E49" s="16" t="n">
+        <v>0.0038</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2673400</v>
+        <v>3639600</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.08</v>
+        <v>0.38</v>
       </c>
       <c r="H49" t="n">
-        <v>46.04</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.37</v>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.452</v>
+        <v>2.705</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.47</v>
+        <v>2.75</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2705,28 +2713,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>-0.0103</v>
+        <v>0.185</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>2616200</v>
+        <v>3516400</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.41</v>
+        <v>0.2</v>
       </c>
       <c r="H50" t="n">
-        <v>44.16</v>
+        <v>49.14</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2734,10 +2742,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.491</v>
+        <v>0.185</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.509</v>
+        <v>0.187</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2750,28 +2758,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>3.97</v>
+        <v>1.56</v>
       </c>
       <c r="E51" s="16" t="n">
-        <v>0.0258</v>
+        <v>0.0331</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>2473700</v>
+        <v>3399300</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.39</v>
+        <v>0.23</v>
       </c>
       <c r="H51" t="n">
-        <v>57.13</v>
+        <v>45.11</v>
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
@@ -2779,10 +2787,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>3.856</v>
+        <v>1.556</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>3.42</v>
+        <v>1.808</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2795,39 +2803,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.925</v>
+        <v>6.61</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>-0.0212</v>
+        <v>-0.0364</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>2465600</v>
+        <v>3086100</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.21</v>
+        <v>0.54</v>
       </c>
       <c r="H52" t="n">
-        <v>40.72</v>
-      </c>
-      <c r="I52" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.87</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.982</v>
+        <v>6.464</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.997</v>
+        <v>6.073</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2840,39 +2848,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>4.93</v>
+        <v>0.36</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>-0.014</v>
+        <v>-0.04</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2385000</v>
+        <v>2975200</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.13</v>
+        <v>1.23</v>
       </c>
       <c r="H53" t="n">
-        <v>53.08</v>
-      </c>
-      <c r="I53" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.95</v>
+      </c>
+      <c r="I53" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>4.904</v>
+        <v>0.379</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>4.804</v>
+        <v>0.385</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2885,28 +2893,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1.16</v>
+        <v>0.395</v>
       </c>
       <c r="E54" s="16" t="n">
-        <v>0.0175</v>
+        <v>0.0128</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2270700</v>
+        <v>2965700</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.23</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>39.28</v>
+        <v>41.24</v>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
@@ -2914,10 +2922,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>1.187</v>
+        <v>0.413</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1.265</v>
+        <v>0.438</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2930,28 +2938,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.9</v>
+        <v>0.44</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>-0.005500000000000001</v>
+        <v>-0.0222</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2238300</v>
+        <v>2866900</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>1.12</v>
+        <v>0.09</v>
       </c>
       <c r="H55" t="n">
-        <v>49.6</v>
+        <v>44.62</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2959,10 +2967,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.904</v>
+        <v>0.452</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.899</v>
+        <v>0.47</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2975,28 +2983,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>0.0153</v>
+        <v>0.905</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2190600</v>
+        <v>2842000</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.87</v>
+        <v>1.42</v>
       </c>
       <c r="H56" t="n">
-        <v>64.3</v>
+        <v>50.77</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3004,10 +3012,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.644</v>
+        <v>0.904</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.633</v>
+        <v>0.899</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3020,39 +3028,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>0.0263</v>
+        <v>0.48</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2163300</v>
+        <v>2825500</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.6</v>
+        <v>0.44</v>
       </c>
       <c r="H57" t="n">
-        <v>54.49</v>
-      </c>
-      <c r="I57" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.16</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>2.3</v>
+        <v>0.491</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>2.231</v>
+        <v>0.509</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3065,39 +3073,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>-0.0171</v>
+        <v>1.26</v>
+      </c>
+      <c r="E58" s="16" t="n">
+        <v>0.0328</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2156700</v>
+        <v>2806500</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.24</v>
+        <v>0.34</v>
       </c>
       <c r="H58" t="n">
-        <v>44.03</v>
-      </c>
-      <c r="I58" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.06</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.601</v>
+        <v>1.274</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.619</v>
+        <v>1.459</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3110,39 +3118,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>6.74</v>
+        <v>0.925</v>
       </c>
       <c r="E59" s="10" t="n">
-        <v>-0.0175</v>
+        <v>-0.0212</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2111600</v>
+        <v>2684000</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.37</v>
+        <v>0.23</v>
       </c>
       <c r="H59" t="n">
-        <v>57.59</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.72</v>
+      </c>
+      <c r="I59" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>6.476</v>
+        <v>0.982</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>6.076</v>
+        <v>0.997</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3155,39 +3163,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>-0.003</v>
+        <v>1.15</v>
+      </c>
+      <c r="E60" s="16" t="n">
+        <v>0.008800000000000001</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2080400</v>
+        <v>2682900</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="H60" t="n">
-        <v>46.63</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.51</v>
+      </c>
+      <c r="I60" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>9.992000000000001</v>
+        <v>1.186</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>10.088</v>
+        <v>1.265</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3200,28 +3208,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="E61" s="16" t="n">
-        <v>0.0016</v>
+        <v>9.98</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>-0.002</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2017500</v>
+        <v>2642000</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="H61" t="n">
-        <v>45.54</v>
+        <v>47.36</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3229,10 +3237,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>6.329</v>
+        <v>9.993</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>6.568</v>
+        <v>10.088</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3245,39 +3253,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>2.62</v>
+        <v>0.575</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>-0.0224</v>
+        <v>-0.0171</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1797400</v>
+        <v>2638700</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="H62" t="n">
-        <v>51.14</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.03</v>
+      </c>
+      <c r="I62" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>2.612</v>
+        <v>0.601</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>2.597</v>
+        <v>0.619</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3290,28 +3298,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>1.25</v>
+        <v>3.96</v>
       </c>
       <c r="E63" s="16" t="n">
-        <v>0.0246</v>
+        <v>0.0233</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1796900</v>
+        <v>2531900</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="H63" t="n">
-        <v>41.68</v>
+        <v>56.86</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3319,10 +3327,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>1.273</v>
+        <v>3.855</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>1.459</v>
+        <v>3.42</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3335,28 +3343,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>-0.0191</v>
+        <v>2.34</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1787700</v>
+        <v>2352800</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.25</v>
+        <v>0.65</v>
       </c>
       <c r="H64" t="n">
-        <v>49.61</v>
+        <v>54.49</v>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
@@ -3364,10 +3372,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.771</v>
+        <v>2.3</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.771</v>
+        <v>2.231</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3380,28 +3388,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>0</v>
+        <v>5.35</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1787300</v>
+        <v>2327200</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>1.42</v>
+        <v>0.14</v>
       </c>
       <c r="H65" t="n">
-        <v>45.53</v>
+        <v>48.92</v>
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
@@ -3409,10 +3417,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.223</v>
+        <v>5.354</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.229</v>
+        <v>5.54</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3425,39 +3433,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.385</v>
+        <v>0.665</v>
       </c>
       <c r="E66" s="16" t="n">
-        <v>0.0132</v>
+        <v>0.0153</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1777000</v>
+        <v>2299600</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="H66" t="n">
-        <v>32.17</v>
-      </c>
-      <c r="I66" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.3</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.428</v>
+        <v>0.644</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.45</v>
+        <v>0.633</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3470,39 +3478,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="E67" s="16" t="n">
-        <v>0.0038</v>
+        <v>0.28</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1768700</v>
+        <v>2261900</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="H67" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.68</v>
+      </c>
+      <c r="I67" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>5.351</v>
+        <v>0.305</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>5.539</v>
+        <v>0.35</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3515,28 +3523,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E68" s="17" t="n">
-        <v>0</v>
+        <v>0.775</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1763200</v>
+        <v>2199200</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="H68" t="n">
-        <v>32.68</v>
+        <v>51.24</v>
       </c>
       <c r="I68" s="15" t="inlineStr">
         <is>
@@ -3544,10 +3552,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.305</v>
+        <v>0.772</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.35</v>
+        <v>0.771</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3560,39 +3568,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>-0.0148</v>
+        <v>0.39</v>
+      </c>
+      <c r="E69" s="16" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1659000</v>
+        <v>2192500</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.36</v>
+        <v>1.02</v>
       </c>
       <c r="H69" t="n">
-        <v>61.63</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.41</v>
+      </c>
+      <c r="I69" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.616</v>
+        <v>0.428</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.589</v>
+        <v>0.45</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3605,31 +3613,40 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BPROP</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>0</v>
+        <v>2.61</v>
+      </c>
+      <c r="E70" s="16" t="n">
+        <v>0.0398</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1631500</v>
-      </c>
-      <c r="G70" s="12" t="n"/>
-      <c r="I70" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J70" s="9" t="n"/>
-      <c r="K70" s="9" t="n"/>
+        <v>1993300</v>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H70" t="n">
+        <v>59.24</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>2.487</v>
+      </c>
+      <c r="K70" s="9" t="n">
+        <v>2.603</v>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
     </row>
@@ -3641,28 +3658,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="E71" s="16" t="n">
-        <v>0.0199</v>
+        <v>2.63</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>-0.0187</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1623600</v>
+        <v>1957600</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.11</v>
+        <v>0.36</v>
       </c>
       <c r="H71" t="n">
-        <v>43.01</v>
+        <v>52.05</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
@@ -3670,10 +3687,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>1.554</v>
+        <v>2.613</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>1.808</v>
+        <v>2.597</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3686,39 +3703,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E72" s="17" t="n">
-        <v>0</v>
+        <v>2.08</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1620800</v>
+        <v>1918700</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="H72" t="n">
-        <v>49.59</v>
-      </c>
-      <c r="I72" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.25</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.866</v>
+        <v>2.102</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.861</v>
+        <v>2.116</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3731,39 +3748,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.45</v>
+        <v>0.625</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>-0.0426</v>
+        <v>-0.053</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1616600</v>
+        <v>1888500</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="H73" t="n">
-        <v>42.73</v>
-      </c>
-      <c r="I73" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.17</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.483</v>
+        <v>0.593</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.475</v>
+        <v>0.503</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3776,39 +3793,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E74" s="17" t="n">
-        <v>0</v>
+        <v>0.665</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>-0.0148</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1589600</v>
+        <v>1792500</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.58</v>
+        <v>0.39</v>
       </c>
       <c r="H74" t="n">
-        <v>31.62</v>
-      </c>
-      <c r="I74" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.63</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.823</v>
+        <v>0.616</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.851</v>
+        <v>0.589</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3821,28 +3838,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.09</v>
+        <v>0.22</v>
       </c>
       <c r="E75" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1576500</v>
+        <v>1787300</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.18</v>
+        <v>1.42</v>
       </c>
       <c r="H75" t="n">
-        <v>47.16</v>
+        <v>45.53</v>
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
@@ -3850,10 +3867,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.103</v>
+        <v>0.223</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2.116</v>
+        <v>0.229</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3866,28 +3883,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E76" s="17" t="n">
-        <v>0</v>
+        <v>0.96</v>
+      </c>
+      <c r="E76" s="16" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1561600</v>
+        <v>1778200</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="H76" t="n">
-        <v>32.88</v>
+        <v>61.59</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -3895,10 +3912,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.466</v>
+        <v>0.91</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.574</v>
+        <v>0.952</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3911,28 +3928,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>-0.033</v>
+        <v>4.22</v>
+      </c>
+      <c r="E77" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1553200</v>
+        <v>1775900</v>
       </c>
       <c r="G77" s="12" t="n">
         <v>0.22</v>
       </c>
       <c r="H77" t="n">
-        <v>52.81</v>
+        <v>60.06</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3940,10 +3957,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.433</v>
+        <v>4.059</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.417</v>
+        <v>3.729</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3956,40 +3973,31 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>BPROP</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>-0.0455</v>
+        <v>0.25</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1551600</v>
-      </c>
-      <c r="G78" s="12" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H78" t="n">
-        <v>57.95</v>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J78" s="9" t="n">
-        <v>0.594</v>
-      </c>
-      <c r="K78" s="9" t="n">
-        <v>0.503</v>
-      </c>
+        <v>1724000</v>
+      </c>
+      <c r="G78" s="12" t="n"/>
+      <c r="I78" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="n"/>
+      <c r="K78" s="9" t="n"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
     </row>
@@ -4001,28 +4009,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>1.26</v>
+        <v>0.455</v>
       </c>
       <c r="E79" s="10" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0319</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1511500</v>
+        <v>1723200</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="H79" t="n">
-        <v>54.42</v>
+        <v>43.61</v>
       </c>
       <c r="I79" s="15" t="inlineStr">
         <is>
@@ -4030,10 +4038,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>1.246</v>
+        <v>0.483</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>1.216</v>
+        <v>0.475</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4046,28 +4054,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E80" s="16" t="n">
-        <v>0.0303</v>
+        <v>0.44</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>-0.033</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1388000</v>
+        <v>1667300</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.89</v>
+        <v>0.24</v>
       </c>
       <c r="H80" t="n">
-        <v>59.3</v>
+        <v>52.81</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4075,10 +4083,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.322</v>
+        <v>0.433</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.33</v>
+        <v>0.417</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4100,19 +4108,19 @@
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="E81" s="16" t="n">
-        <v>0.0141</v>
+        <v>0.0423</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1314900</v>
+        <v>1664900</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>3.54</v>
+        <v>4.49</v>
       </c>
       <c r="H81" t="n">
-        <v>73.81</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
@@ -4120,7 +4128,7 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.321</v>
+        <v>0.322</v>
       </c>
       <c r="K81" s="9" t="n">
         <v>0.301</v>
@@ -4136,39 +4144,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="E82" s="16" t="n">
-        <v>0.0221</v>
+        <v>0.865</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1307700</v>
+        <v>1620800</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.51</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H82" t="n">
-        <v>51.65</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.59</v>
+      </c>
+      <c r="I82" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>1.365</v>
+        <v>0.866</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>1.424</v>
+        <v>0.861</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4181,39 +4189,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>-0.0204</v>
+        <v>0.805</v>
+      </c>
+      <c r="E83" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1307100</v>
+        <v>1600500</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.4</v>
+        <v>0.59</v>
       </c>
       <c r="H83" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="I83" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.62</v>
+      </c>
+      <c r="I83" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>2.991</v>
+        <v>0.823</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>2.883</v>
+        <v>0.851</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4226,28 +4234,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SCGM</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E84" s="17" t="n">
-        <v>0</v>
+        <v>0.435</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>-0.0114</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1298200</v>
+        <v>1581000</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>1.66</v>
+        <v>0.11</v>
       </c>
       <c r="H84" t="n">
-        <v>66.39</v>
+        <v>31.89</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -4255,10 +4263,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.349</v>
+        <v>0.466</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.332</v>
+        <v>0.574</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4271,28 +4279,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.74</v>
+        <v>1.25</v>
       </c>
       <c r="E85" s="10" t="n">
-        <v>-0.0067</v>
+        <v>-0.0157</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1275500</v>
+        <v>1521200</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.38</v>
+        <v>0.24</v>
       </c>
       <c r="H85" t="n">
-        <v>50.46</v>
+        <v>52.84</v>
       </c>
       <c r="I85" s="15" t="inlineStr">
         <is>
@@ -4300,10 +4308,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.745</v>
+        <v>1.245</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.709</v>
+        <v>1.216</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4316,39 +4324,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E86" s="10" t="n">
-        <v>-0.0196</v>
+        <v>0.63</v>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1275400</v>
+        <v>1413000</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.23</v>
+        <v>0.39</v>
       </c>
       <c r="H86" t="n">
-        <v>42.78</v>
-      </c>
-      <c r="I86" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.48999999999999</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.261</v>
+        <v>0.624</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.276</v>
+        <v>0.614</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4361,33 +4369,40 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.71</v>
+        <v>0.25</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>-0.0207</v>
+        <v>-0.0196</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1261300</v>
+        <v>1394800</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.05</v>
+        <v>0.26</v>
+      </c>
+      <c r="H87" t="n">
+        <v>42.78</v>
       </c>
       <c r="I87" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J87" s="9" t="n"/>
-      <c r="K87" s="9" t="n"/>
+      <c r="J87" s="9" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>0.276</v>
+      </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
     </row>
@@ -4399,28 +4414,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>4.2</v>
+        <v>2.87</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>-0.004699999999999999</v>
+        <v>-0.0238</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1255000</v>
+        <v>1393800</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.16</v>
+        <v>0.42</v>
       </c>
       <c r="H88" t="n">
-        <v>59.06</v>
+        <v>45.32</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -4428,10 +4443,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>4.057</v>
+        <v>2.99</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>3.728</v>
+        <v>2.883</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4444,28 +4459,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>2.16</v>
+        <v>0.34</v>
       </c>
       <c r="E89" s="16" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.0303</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1231700</v>
+        <v>1388000</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.19</v>
+        <v>0.89</v>
       </c>
       <c r="H89" t="n">
-        <v>71.15000000000001</v>
+        <v>59.3</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -4473,10 +4488,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>2.021</v>
+        <v>0.322</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>1.977</v>
+        <v>0.33</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4489,40 +4504,33 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>1.29</v>
+        <v>0.71</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>-0.0373</v>
+        <v>-0.0207</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1225400</v>
+        <v>1376600</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="H90" t="n">
-        <v>51.98</v>
+        <v>0.05</v>
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J90" s="9" t="n">
-        <v>1.289</v>
-      </c>
-      <c r="K90" s="9" t="n">
-        <v>1.199</v>
-      </c>
+      <c r="J90" s="9" t="n"/>
+      <c r="K90" s="9" t="n"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
     </row>
@@ -4534,28 +4542,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2.58</v>
+        <v>2.16</v>
       </c>
       <c r="E91" s="16" t="n">
-        <v>0.0279</v>
+        <v>0.009300000000000001</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1220100</v>
+        <v>1372000</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="H91" t="n">
-        <v>56.93</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
@@ -4563,10 +4571,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>2.485</v>
+        <v>2.021</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>2.602</v>
+        <v>1.977</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4579,28 +4587,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>-0.0227</v>
+        <v>0.745</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1194400</v>
+        <v>1354800</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.13</v>
+        <v>0.4</v>
       </c>
       <c r="H92" t="n">
-        <v>40.59</v>
+        <v>51.5</v>
       </c>
       <c r="I92" s="15" t="inlineStr">
         <is>
@@ -4608,10 +4616,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.221</v>
+        <v>0.745</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.257</v>
+        <v>0.709</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4624,39 +4632,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>-0.0413</v>
+        <v>1.4</v>
+      </c>
+      <c r="E93" s="16" t="n">
+        <v>0.0294</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1141100</v>
+        <v>1352200</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.15</v>
+        <v>0.53</v>
       </c>
       <c r="H93" t="n">
-        <v>36.36</v>
-      </c>
-      <c r="I93" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.99</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.631</v>
+        <v>1.366</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.673</v>
+        <v>1.425</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4669,39 +4677,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E94" s="16" t="n">
-        <v>0.0192</v>
+        <v>0.55</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1105300</v>
+        <v>1343000</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.14</v>
+        <v>0.59</v>
       </c>
       <c r="H94" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.68</v>
+      </c>
+      <c r="I94" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.267</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.287</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4714,39 +4722,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="E95" s="10" t="n">
-        <v>-0.0184</v>
+        <v>-0.0299</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1073500</v>
+        <v>1331200</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.17</v>
+        <v>0.48</v>
       </c>
       <c r="H95" t="n">
-        <v>43.24</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.98</v>
+      </c>
+      <c r="I95" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>1.644</v>
+        <v>1.289</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>1.727</v>
+        <v>1.199</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4759,28 +4767,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>SCGM</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>-0.0083</v>
+        <v>0.365</v>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1072700</v>
+        <v>1319400</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.72</v>
+        <v>1.69</v>
       </c>
       <c r="H96" t="n">
-        <v>64.72</v>
+        <v>66.39</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -4788,10 +4796,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>2.183</v>
+        <v>0.349</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>2.219</v>
+        <v>0.332</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4804,28 +4812,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E97" s="16" t="n">
-        <v>0.0106</v>
+        <v>1.68</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>-0.0059</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1041700</v>
+        <v>1262400</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="H97" t="n">
-        <v>59.55</v>
+        <v>55.61</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -4833,10 +4841,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.909</v>
+        <v>1.639</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.952</v>
+        <v>1.665</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4849,39 +4857,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>3.88</v>
+        <v>0.585</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>-0.0177</v>
+        <v>-0.0331</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>968600</v>
+        <v>1238900</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="H98" t="n">
-        <v>52.41</v>
-      </c>
-      <c r="I98" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.14</v>
+      </c>
+      <c r="I98" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>3.852</v>
+        <v>0.631</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>3.785</v>
+        <v>0.673</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4894,28 +4902,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CITAGLB</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E99" s="16" t="n">
-        <v>0.045</v>
+        <v>0.82</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>-0.0353</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>935800</v>
+        <v>1226200</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>3.75</v>
+        <v>0.2</v>
       </c>
       <c r="H99" t="n">
-        <v>67.01000000000001</v>
+        <v>41.35</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -4923,10 +4931,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>1.064</v>
+        <v>0.873</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>1.051</v>
+        <v>0.87</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4939,39 +4947,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="E100" s="16" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.215</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>932500</v>
+        <v>1204600</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="H100" t="n">
-        <v>55.41</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.59</v>
+      </c>
+      <c r="I100" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>4.492</v>
+        <v>0.221</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>4.449</v>
+        <v>0.257</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4984,28 +4992,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>-0.0394</v>
+        <v>0.265</v>
+      </c>
+      <c r="E101" s="16" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>921000</v>
+        <v>1172400</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="H101" t="n">
-        <v>60.48</v>
+        <v>44.9</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -5013,10 +5021,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>1.147</v>
+        <v>0.267</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>1.009</v>
+        <v>0.287</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5029,28 +5037,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.75</v>
+        <v>1.6</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>-0.0323</v>
+        <v>-0.0184</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>911900</v>
+        <v>1115400</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H102" t="n">
-        <v>51.76</v>
+        <v>43.24</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -5058,10 +5066,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.75</v>
+        <v>1.644</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.702</v>
+        <v>1.727</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5074,39 +5082,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.83</v>
+        <v>2.37</v>
       </c>
       <c r="E103" s="10" t="n">
-        <v>-0.0119</v>
+        <v>-0.0125</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>849000</v>
+        <v>1101700</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.31</v>
+        <v>0.74</v>
       </c>
       <c r="H103" t="n">
-        <v>36.07</v>
-      </c>
-      <c r="I103" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.83</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.857</v>
+        <v>2.182</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.913</v>
+        <v>2.218</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5119,28 +5127,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.62</v>
+        <v>3.88</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>-0.0313</v>
+        <v>-0.0177</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>837700</v>
+        <v>1068500</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="H104" t="n">
-        <v>64.22</v>
+        <v>52.41</v>
       </c>
       <c r="I104" s="13" t="inlineStr">
         <is>
@@ -5148,10 +5156,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>3.852</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.498</v>
+        <v>3.785</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5164,39 +5172,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>-0.0301</v>
+        <v>4.63</v>
+      </c>
+      <c r="E105" s="16" t="n">
+        <v>0.0131</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>807500</v>
+        <v>1063400</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="H105" t="n">
-        <v>41.17</v>
-      </c>
-      <c r="I105" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.08</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.698</v>
+        <v>4.494</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.6929999999999999</v>
+        <v>4.45</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5209,39 +5217,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="E106" s="16" t="n">
-        <v>0.0044</v>
+        <v>0.245</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>-0.0392</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>789200</v>
+        <v>1023500</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="H106" t="n">
-        <v>42.63</v>
-      </c>
-      <c r="I106" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.26</v>
+      </c>
+      <c r="I106" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>6.98</v>
+        <v>0.263</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>7.415</v>
+        <v>0.268</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5254,28 +5262,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0336</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>WINSTAR</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E107" s="16" t="n">
-        <v>0.024</v>
+        <v>1.22</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>-0.0394</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>782500</v>
+        <v>1016400</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>1.57</v>
+        <v>0.19</v>
       </c>
       <c r="H107" t="n">
-        <v>55.55</v>
+        <v>60.48</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -5283,10 +5291,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.635</v>
+        <v>1.147</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.648</v>
+        <v>1.009</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5299,28 +5307,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.825</v>
+        <v>0.755</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>-0.0294</v>
+        <v>-0.0258</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>763200</v>
+        <v>1013000</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="H108" t="n">
-        <v>41.94</v>
+        <v>52.71</v>
       </c>
       <c r="I108" s="13" t="inlineStr">
         <is>
@@ -5328,10 +5336,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.874</v>
+        <v>0.75</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.87</v>
+        <v>0.702</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5344,39 +5352,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.59</v>
+        <v>2.05</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>-0.0328</v>
+        <v>-0.0049</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>752300</v>
+        <v>995700</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="H109" t="n">
-        <v>56.67</v>
-      </c>
-      <c r="I109" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.53</v>
+      </c>
+      <c r="I109" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>2.04</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.535</v>
+        <v>2.058</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5389,28 +5397,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>7.35</v>
+        <v>0.62</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>-0.038</v>
+        <v>-0.0313</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>746400</v>
+        <v>980600</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="H110" t="n">
-        <v>51.27</v>
+        <v>64.22</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
@@ -5418,10 +5426,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>7.359</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>7.01</v>
+        <v>0.498</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5434,39 +5442,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>2.46</v>
+        <v>0.83</v>
       </c>
       <c r="E111" s="10" t="n">
-        <v>-0.016</v>
+        <v>-0.0119</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>740000</v>
+        <v>955500</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.13</v>
+        <v>0.35</v>
       </c>
       <c r="H111" t="n">
-        <v>40.71</v>
-      </c>
-      <c r="I111" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.07</v>
+      </c>
+      <c r="I111" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>2.604</v>
+        <v>0.857</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>2.799</v>
+        <v>0.913</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5488,19 +5496,19 @@
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E112" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>1.29</v>
+      </c>
+      <c r="E112" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>736600</v>
+        <v>942000</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="H112" t="n">
-        <v>53.42</v>
+        <v>56.76</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -5508,7 +5516,7 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>1.27</v>
+        <v>1.271</v>
       </c>
       <c r="K112" s="9" t="n">
         <v>1.27</v>
@@ -5524,28 +5532,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>CITAGLB</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>-0.0059</v>
+        <v>1.16</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>0.045</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>689000</v>
+        <v>936400</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.09</v>
+        <v>3.75</v>
       </c>
       <c r="H113" t="n">
-        <v>55.61</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -5553,10 +5561,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>1.639</v>
+        <v>1.064</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>1.665</v>
+        <v>1.051</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5569,39 +5577,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>1.13</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>-0.0259</v>
+        <v>-0.0072</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>674000</v>
+        <v>932500</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="H114" t="n">
-        <v>54.62</v>
-      </c>
-      <c r="I114" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.27</v>
+      </c>
+      <c r="I114" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>1.113</v>
+        <v>0.706</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.964</v>
+        <v>0.757</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5614,28 +5622,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PANTECH</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E115" s="17" t="n">
-        <v>0</v>
+        <v>7.38</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>-0.034</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>664400</v>
+        <v>931400</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>1.54</v>
+        <v>0.22</v>
       </c>
       <c r="H115" t="n">
-        <v>68.33</v>
+        <v>51.96</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
@@ -5643,10 +5651,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.665</v>
+        <v>7.362</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.662</v>
+        <v>7.01</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5659,39 +5667,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="E116" s="16" t="n">
-        <v>0.0013</v>
+        <v>1.01</v>
+      </c>
+      <c r="E116" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>646600</v>
+        <v>930400</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.06</v>
+        <v>1.49</v>
       </c>
       <c r="H116" t="n">
-        <v>50.57</v>
-      </c>
-      <c r="I116" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.68</v>
+      </c>
+      <c r="I116" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>7.417</v>
+        <v>1.011</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>7.734</v>
+        <v>0.992</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5704,28 +5712,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.635</v>
+        <v>7.47</v>
       </c>
       <c r="E117" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>625200</v>
+        <v>917500</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.43</v>
+        <v>0.09</v>
       </c>
       <c r="H117" t="n">
-        <v>60.22</v>
+        <v>49.96</v>
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
@@ -5733,10 +5741,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.619</v>
+        <v>7.416</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.554</v>
+        <v>7.734</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5749,28 +5757,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E118" s="10" t="n">
-        <v>-0.0216</v>
+        <v>6.87</v>
+      </c>
+      <c r="E118" s="16" t="n">
+        <v>0.0015</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>622500</v>
+        <v>914300</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="H118" t="n">
-        <v>37.77</v>
+        <v>41.73</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5778,10 +5786,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.705</v>
+        <v>6.978</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.757</v>
+        <v>7.415</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5794,39 +5802,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E119" s="10" t="n">
-        <v>-0.009000000000000001</v>
+        <v>0.64</v>
+      </c>
+      <c r="E119" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>608000</v>
+        <v>896000</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.27</v>
+        <v>0.91</v>
       </c>
       <c r="H119" t="n">
-        <v>42.68</v>
-      </c>
-      <c r="I119" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.13</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.636</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.634</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5839,39 +5847,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0336</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>WINSTAR</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>-0.009899999999999999</v>
+        <v>0.635</v>
+      </c>
+      <c r="E120" s="16" t="n">
+        <v>0.016</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>602800</v>
+        <v>872500</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.96</v>
+        <v>1.75</v>
       </c>
       <c r="H120" t="n">
-        <v>45.82</v>
-      </c>
-      <c r="I120" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.89</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>1.01</v>
+        <v>0.635</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.992</v>
+        <v>0.648</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5884,28 +5892,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="E121" s="10" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0431</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>596900</v>
+        <v>870900</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.14</v>
+        <v>0.29</v>
       </c>
       <c r="H121" t="n">
-        <v>22.18</v>
+        <v>52.38</v>
       </c>
       <c r="I121" s="15" t="inlineStr">
         <is>
@@ -5913,10 +5921,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>1.395</v>
+        <v>1.111</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>1.444</v>
+        <v>0.963</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5929,39 +5937,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SENTRAL</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.6</v>
+        <v>0.585</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>-0.0083</v>
+        <v>-0.04099999999999999</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>579400</v>
+        <v>815100</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>1.33</v>
+        <v>0.17</v>
       </c>
       <c r="H122" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="I122" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.59</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.624</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.648</v>
+        <v>0.535</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5974,39 +5982,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E123" s="17" t="n">
-        <v>0</v>
+        <v>0.645</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>-0.0301</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>576000</v>
+        <v>807500</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.59</v>
+        <v>0.18</v>
       </c>
       <c r="H123" t="n">
-        <v>58.13</v>
-      </c>
-      <c r="I123" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.17</v>
+      </c>
+      <c r="I123" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.636</v>
+        <v>0.698</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.634</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6019,39 +6027,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>BAT</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="E124" s="10" t="n">
-        <v>-0.0604</v>
+        <v>2.24</v>
+      </c>
+      <c r="E124" s="16" t="n">
+        <v>0.0136</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>573900</v>
+        <v>790900</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>4.22</v>
+        <v>0.32</v>
       </c>
       <c r="H124" t="n">
-        <v>29.35</v>
-      </c>
-      <c r="I124" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.61</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>4.174</v>
+        <v>2.147</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>4.334</v>
+        <v>2.093</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6064,39 +6072,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1.44</v>
+        <v>2.7</v>
       </c>
       <c r="E125" s="10" t="n">
-        <v>-0.027</v>
+        <v>-0.0074</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>560700</v>
+        <v>790700</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.78</v>
+        <v>0.22</v>
       </c>
       <c r="H125" t="n">
-        <v>44.15</v>
-      </c>
-      <c r="I125" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.72</v>
+      </c>
+      <c r="I125" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>1.465</v>
+        <v>2.797</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>1.569</v>
+        <v>2.929</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6109,28 +6117,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.89</v>
+        <v>2.46</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>-0.005600000000000001</v>
+        <v>-0.016</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>556800</v>
+        <v>771500</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.38</v>
+        <v>0.13</v>
       </c>
       <c r="H126" t="n">
-        <v>36.93</v>
+        <v>40.71</v>
       </c>
       <c r="I126" s="13" t="inlineStr">
         <is>
@@ -6138,10 +6146,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.914</v>
+        <v>2.604</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.971</v>
+        <v>2.799</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6154,28 +6162,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>5.74</v>
+        <v>1.27</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>-0.0255</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>550100</v>
+        <v>748900</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="H127" t="n">
-        <v>55.53</v>
+        <v>22.18</v>
       </c>
       <c r="I127" s="15" t="inlineStr">
         <is>
@@ -6183,10 +6191,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>5.596</v>
+        <v>1.395</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>5.408</v>
+        <v>1.444</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6199,28 +6207,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>1.24</v>
+        <v>10.78</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>-0.008</v>
+        <v>-0.0218</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>549100</v>
+        <v>741600</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="H128" t="n">
-        <v>50.64</v>
+        <v>55.93</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6228,10 +6236,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>1.254</v>
+        <v>10.619</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1.142</v>
+        <v>9.999000000000001</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6244,28 +6252,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="E129" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>537600</v>
+        <v>740400</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.67</v>
+        <v>0.35</v>
       </c>
       <c r="H129" t="n">
-        <v>32.37</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
@@ -6273,10 +6281,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>1.672</v>
+        <v>1.388</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>1.752</v>
+        <v>1.357</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6289,39 +6297,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>PANTECH</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E130" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>708400</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H130" t="n">
+        <v>68.33</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="n">
         <v>0.665</v>
       </c>
-      <c r="E130" s="10" t="n">
-        <v>-0.0221</v>
-      </c>
-      <c r="F130" s="11" t="n">
-        <v>527400</v>
-      </c>
-      <c r="G130" s="12" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H130" t="n">
-        <v>54.19</v>
-      </c>
-      <c r="I130" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J130" s="9" t="n">
-        <v>0.66</v>
-      </c>
       <c r="K130" s="9" t="n">
-        <v>0.596</v>
+        <v>0.662</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6334,28 +6342,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>10.8</v>
+        <v>1.22</v>
       </c>
       <c r="E131" s="10" t="n">
-        <v>-0.02</v>
+        <v>-0.06150000000000001</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>522800</v>
+        <v>693100</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="H131" t="n">
-        <v>56.36</v>
+        <v>41.62</v>
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
@@ -6363,10 +6371,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>10.621</v>
+        <v>1.291</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>9.999000000000001</v>
+        <v>1.315</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6379,28 +6387,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E132" s="16" t="n">
-        <v>0.0063</v>
+        <v>5.74</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>-0.0255</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>513500</v>
+        <v>684400</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="H132" t="n">
-        <v>28.6</v>
+        <v>55.53</v>
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
@@ -6408,10 +6416,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.851</v>
+        <v>5.596</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>1.009</v>
+        <v>5.408</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6424,28 +6432,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1.23</v>
+        <v>6.85</v>
       </c>
       <c r="E133" s="10" t="n">
-        <v>-0.0538</v>
+        <v>-0.0072</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>511200</v>
+        <v>666600</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.28</v>
+        <v>0.11</v>
       </c>
       <c r="H133" t="n">
-        <v>42.54</v>
+        <v>51.13</v>
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
@@ -6453,10 +6461,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>1.291</v>
+        <v>6.844</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>1.315</v>
+        <v>6.829</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6469,28 +6477,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E134" s="17" t="n">
-        <v>0</v>
+        <v>5.8</v>
+      </c>
+      <c r="E134" s="16" t="n">
+        <v>0.0052</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>508600</v>
+        <v>661500</v>
       </c>
       <c r="G134" s="12" t="n">
         <v>0.08</v>
       </c>
       <c r="H134" t="n">
-        <v>45.91</v>
+        <v>46</v>
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
@@ -6498,16 +6506,916 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>1.267</v>
+        <v>5.807</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>1.319</v>
+        <v>6.029</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>652600</v>
+      </c>
+      <c r="G135" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H135" t="n">
+        <v>54.84</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>5.088</v>
+      </c>
+      <c r="K135" s="9" t="n">
+        <v>5.033</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="14" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>-0.0033</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>649700</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H136" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="I136" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>3.224</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>645500</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H137" t="n">
+        <v>49.73</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>1.253</v>
+      </c>
+      <c r="K137" s="9" t="n">
+        <v>1.142</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="14" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>PGLOBAL</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E138" s="16" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>639500</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H138" t="n">
+        <v>61.45</v>
+      </c>
+      <c r="I138" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>-0.0238</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>635300</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H139" t="n">
+        <v>43.59</v>
+      </c>
+      <c r="I139" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="K139" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="14" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E140" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>633200</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H140" t="n">
+        <v>38.17</v>
+      </c>
+      <c r="I140" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="E141" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>623200</v>
+      </c>
+      <c r="G141" s="12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H141" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="K141" s="9" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="14" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>4162</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>619900</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="H142" t="n">
+        <v>28.02</v>
+      </c>
+      <c r="I142" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="K142" s="9" t="n">
+        <v>4.334</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>-0.0236</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>617700</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H143" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="K143" s="9" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="14" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>5123</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>SENTRAL</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>-0.0083</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>614800</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H144" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="I144" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>-0.0141</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>610000</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H145" t="n">
+        <v>58.23</v>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="n">
+        <v>1.325</v>
+      </c>
+      <c r="K145" s="9" t="n">
+        <v>1.264</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="14" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E146" s="16" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>607100</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H146" t="n">
+        <v>56.91</v>
+      </c>
+      <c r="I146" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>5335</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>HI</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E147" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>606400</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H147" t="n">
+        <v>32.37</v>
+      </c>
+      <c r="I147" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="n">
+        <v>1.672</v>
+      </c>
+      <c r="K147" s="9" t="n">
+        <v>1.752</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="14" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>0168</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>BMGREEN</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>570200</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H148" t="n">
+        <v>44.15</v>
+      </c>
+      <c r="I148" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="n">
+        <v>1.465</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>1.569</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>-0.0208</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>566100</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H149" t="n">
+        <v>46.08</v>
+      </c>
+      <c r="I149" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="K149" s="9" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="14" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E150" s="16" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>539300</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H150" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="I150" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>-0.0221</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>527400</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H151" t="n">
+        <v>54.19</v>
+      </c>
+      <c r="I151" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K151" s="9" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="14" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E152" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>522700</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H152" t="n">
+        <v>45.91</v>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>IOICORP</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="E153" s="16" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>517600</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H153" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="I153" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="K153" s="9" t="n">
+        <v>4.641</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="14" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>0277</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>CLOUDPT</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E154" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>515700</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H154" t="n">
+        <v>55.74</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="K154" s="9" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M134"/>
+  <autoFilter ref="A1:M154"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-30/bursa-report-2026-10-30.xlsx
+++ b/docs/downloads/2026-10-30/bursa-report-2026-10-30.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-30" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-30'!$A$1:$M$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-30'!$A$1:$M$181</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M175"/>
+  <dimension ref="A1:M181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -572,10 +572,10 @@
         <v>0.0247</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1807800</v>
+        <v>1861500</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>72.31999999999999</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号出现，但RSI 72.32已进入超买区，现价0.83高于50日均线0.683约21.5%，短期涨幅偏大，信号可靠性需谨慎看待。</t>
+          <t>SAR转多信号，但RSI 72.32已超买，现价高于50日均线约21.5%，信号可靠性偏弱。</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
         <v>0.0104</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>23312300</v>
+        <v>23313200</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>1.05</v>
@@ -651,7 +651,7 @@
       </c>
       <c r="M3" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 64.95接近超买区，现价高于50日均线约20.6%，技术面偏强。</t>
+          <t>SAR转多信号，RSI 64.95偏高但未超买，现价高于50日均线约20.6%，技术面偏强。</t>
         </is>
       </c>
     </row>
@@ -678,10 +678,10 @@
         <v>-0.1875</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>200380100</v>
+        <v>203425400</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H4" t="n">
         <v>32.78</v>
@@ -723,7 +723,7 @@
         <v>-0.0333</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>89389100</v>
+        <v>89390100</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>1.85</v>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.355</v>
+        <v>0.345</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>-0.3426</v>
+        <v>-0.3611</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>80897600</v>
+        <v>81149800</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="H6" t="n">
-        <v>20.46</v>
+        <v>20.05</v>
       </c>
       <c r="I6" s="15" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.63</v>
+        <v>0.629</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>0.577</v>
@@ -813,7 +813,7 @@
         <v>-0.3784</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>49911800</v>
+        <v>50026100</v>
       </c>
       <c r="G7" s="12" t="n">
         <v>1.2</v>
@@ -858,7 +858,7 @@
         <v>-0.0294</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>34980100</v>
+        <v>35052300</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>0.48</v>
@@ -903,7 +903,7 @@
         <v>-0.0051</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>33013300</v>
+        <v>33351700</v>
       </c>
       <c r="G9" s="12" t="n">
         <v>0.41</v>
@@ -978,28 +978,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AXTERIA</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.16</v>
+        <v>0.865</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>-0.0857</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>14616800</v>
+        <v>14659800</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.54</v>
+        <v>0.68</v>
       </c>
       <c r="H11" t="n">
-        <v>57.77</v>
+        <v>47.49</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.143</v>
+        <v>0.867</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.121</v>
+        <v>0.868</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1023,28 +1023,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>AXTERIA</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.865</v>
+        <v>0.16</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0857</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>14513800</v>
+        <v>14616800</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.68</v>
+        <v>1.54</v>
       </c>
       <c r="H12" t="n">
-        <v>47.49</v>
+        <v>57.77</v>
       </c>
       <c r="I12" s="13" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.867</v>
+        <v>0.143</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.868</v>
+        <v>0.121</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>-0.0314</v>
+        <v>-0.0359</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>13111300</v>
+        <v>13134500</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>0.45</v>
       </c>
       <c r="H13" t="n">
-        <v>60.52</v>
+        <v>59.8</v>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>2.045</v>
+        <v>2.044</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>1.851</v>
@@ -1173,10 +1173,10 @@
         <v>-0.03700000000000001</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>12414900</v>
+        <v>12637100</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="H15" t="n">
         <v>35.76</v>
@@ -1218,10 +1218,10 @@
         <v>0.0435</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>11619600</v>
+        <v>11659600</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="H16" t="n">
         <v>73.88</v>
@@ -1263,10 +1263,10 @@
         <v>0.0021</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>11480400</v>
+        <v>11639100</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="H17" t="n">
         <v>50</v>
@@ -1308,7 +1308,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>11414400</v>
+        <v>11414500</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>0.74</v>
@@ -1347,19 +1347,19 @@
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.24</v>
+        <v>0.235</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>0.1163</v>
+        <v>0.09300000000000001</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>10736400</v>
+        <v>10798700</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="H19" t="n">
-        <v>57.98</v>
+        <v>55.94</v>
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
         <v>0.007800000000000001</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>9862200</v>
+        <v>9932600</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="H20" t="n">
         <v>66.3</v>
@@ -1439,10 +1439,10 @@
         <v>0.008100000000000001</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>9708800</v>
+        <v>9729800</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="H21" t="n">
         <v>68.44</v>
@@ -1484,10 +1484,10 @@
         <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>9335200</v>
+        <v>9440400</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="H22" t="n">
         <v>24.97</v>
@@ -1514,28 +1514,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.645</v>
+        <v>0.82</v>
       </c>
       <c r="E23" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>7774000</v>
+        <v>7807800</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.77</v>
+        <v>0.49</v>
       </c>
       <c r="H23" t="n">
-        <v>66.40000000000001</v>
+        <v>53.09</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
@@ -1543,10 +1543,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.631</v>
+        <v>0.819</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.62</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1559,28 +1559,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.82</v>
+        <v>0.645</v>
       </c>
       <c r="E24" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>7712500</v>
+        <v>7774000</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.48</v>
+        <v>0.77</v>
       </c>
       <c r="H24" t="n">
-        <v>53.09</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.819</v>
+        <v>0.631</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>-0.0269</v>
+        <v>-0.0231</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>7456300</v>
+        <v>7478400</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>0.44</v>
       </c>
       <c r="H25" t="n">
-        <v>45.91</v>
+        <v>46.53</v>
       </c>
       <c r="I25" s="15" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>2.589</v>
+        <v>2.59</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>2.574</v>
@@ -1709,10 +1709,10 @@
         <v>0.1538</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>7168800</v>
+        <v>7259800</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="H27" t="n">
         <v>77.38</v>
@@ -1754,7 +1754,7 @@
         <v>-0.0392</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>7161700</v>
+        <v>7188700</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>0.98</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>6941700</v>
+        <v>7020800</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0.51</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>6.33</v>
+        <v>6.31</v>
       </c>
       <c r="E33" s="17" t="n">
-        <v>0.0048</v>
+        <v>0.0016</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>6133300</v>
+        <v>6142800</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>0.78</v>
       </c>
       <c r="H33" t="n">
-        <v>47.01</v>
+        <v>45.54</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>6.331</v>
+        <v>6.329</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>6.568</v>
@@ -2045,28 +2045,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
+      </c>
+      <c r="E35" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>6070900</v>
+        <v>6085400</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.41</v>
+        <v>0.32</v>
       </c>
       <c r="H35" t="n">
-        <v>55.61</v>
+        <v>36.56</v>
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.051</v>
+        <v>0.203</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.047</v>
+        <v>0.223</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2090,39 +2090,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.38</v>
+        <v>0.055</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>0.0133</v>
+        <v>0.1</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6002700</v>
+        <v>6071000</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.88</v>
+        <v>0.41</v>
       </c>
       <c r="H36" t="n">
-        <v>59.17</v>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.61</v>
+      </c>
+      <c r="I36" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.374</v>
+        <v>0.051</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.37</v>
+        <v>0.047</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2135,39 +2135,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>0</v>
+        <v>0.38</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5983200</v>
+        <v>6002700</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.31</v>
+        <v>0.88</v>
       </c>
       <c r="H37" t="n">
-        <v>36.56</v>
-      </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.17</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.203</v>
+        <v>0.374</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.223</v>
+        <v>0.37</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2189,19 +2189,19 @@
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.575</v>
+        <v>0.58</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>-0.0417</v>
+        <v>-0.0333</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5663800</v>
+        <v>5763800</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="H38" t="n">
-        <v>50.96</v>
+        <v>52.03</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -2240,10 +2240,10 @@
         <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>5565200</v>
+        <v>5593200</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="H39" t="n">
         <v>82.76000000000001</v>
@@ -2285,7 +2285,7 @@
         <v>-0.0333</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>5522900</v>
+        <v>5544900</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0.47</v>
@@ -2330,7 +2330,7 @@
         <v>-0.0175</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>5462800</v>
+        <v>5512800</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>0.46</v>
@@ -2375,10 +2375,10 @@
         <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>5451900</v>
+        <v>5463400</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="H42" t="n">
         <v>53.96</v>
@@ -2405,39 +2405,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>2.18</v>
+        <v>1.15</v>
       </c>
       <c r="E43" s="17" t="n">
-        <v>0.009300000000000001</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>5211000</v>
+        <v>5449600</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="H43" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.51</v>
+      </c>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>2.115</v>
+        <v>1.186</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>2.225</v>
+        <v>1.265</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2450,28 +2450,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>ASTRO</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>1.16</v>
+        <v>0.055</v>
       </c>
       <c r="E44" s="17" t="n">
-        <v>0.0175</v>
+        <v>0.1</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>5094200</v>
+        <v>5389900</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.52</v>
+        <v>1.26</v>
       </c>
       <c r="H44" t="n">
-        <v>39.28</v>
+        <v>50.11</v>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>1.187</v>
+        <v>0.054</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>1.265</v>
+        <v>0.057</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2495,39 +2495,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>2.64</v>
+        <v>2.17</v>
       </c>
       <c r="E45" s="17" t="n">
-        <v>0.0038</v>
+        <v>0.0046</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>4953100</v>
+        <v>5243000</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
       <c r="H45" t="n">
-        <v>42.37</v>
-      </c>
-      <c r="I45" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.25</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>2.705</v>
+        <v>2.114</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>2.75</v>
+        <v>2.224</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2540,28 +2540,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>-0.1314</v>
+        <v>2.64</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>0.0038</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>4923500</v>
+        <v>5024800</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>1.47</v>
+        <v>0.52</v>
       </c>
       <c r="H46" t="n">
-        <v>30.19</v>
+        <v>42.37</v>
       </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>3.016</v>
+        <v>2.705</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.666</v>
+        <v>2.75</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2585,39 +2585,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E47" s="17" t="n">
-        <v>0.0122</v>
+        <v>2.3</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>-0.1606</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>4686800</v>
+        <v>4967900</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.4</v>
+        <v>1.48</v>
       </c>
       <c r="H47" t="n">
-        <v>55.59</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.69</v>
+      </c>
+      <c r="I47" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.404</v>
+        <v>3.008</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.386</v>
+        <v>2.665</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2630,28 +2630,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>-0.0222</v>
+        <v>0.42</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>4619900</v>
+        <v>4716800</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.14</v>
+        <v>0.4</v>
       </c>
       <c r="H48" t="n">
-        <v>44.62</v>
+        <v>57.09</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2659,10 +2659,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.452</v>
+        <v>0.404</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.47</v>
+        <v>0.386</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2684,19 +2684,19 @@
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E49" s="16" t="n">
-        <v>0</v>
+        <v>2.08</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4501000</v>
+        <v>4653000</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="H49" t="n">
-        <v>47.16</v>
+        <v>45.25</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>2.103</v>
+        <v>2.102</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>2.116</v>
@@ -2720,28 +2720,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0129</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SRIDGE</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E50" s="17" t="n">
-        <v>0.0455</v>
+        <v>0.44</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>-0.0222</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>4219600</v>
+        <v>4629500</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>3.76</v>
+        <v>0.14</v>
       </c>
       <c r="H50" t="n">
-        <v>43.81</v>
+        <v>44.62</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.118</v>
+        <v>0.452</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.13</v>
+        <v>0.47</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2765,28 +2765,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>0.0464</v>
+        <v>9.98</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>-0.002</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>4218900</v>
+        <v>4376300</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="H51" t="n">
-        <v>47.07</v>
+        <v>47.36</v>
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
@@ -2794,10 +2794,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>1.558</v>
+        <v>9.993</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>1.809</v>
+        <v>10.088</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2810,28 +2810,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>-0.001</v>
+        <v>1.58</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>0.0464</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4209900</v>
+        <v>4271100</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.37</v>
+        <v>0.29</v>
       </c>
       <c r="H52" t="n">
-        <v>48.11</v>
+        <v>47.07</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>9.994</v>
+        <v>1.558</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>10.088</v>
+        <v>1.809</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2855,28 +2855,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0129</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SRIDGE</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.835</v>
+        <v>0.115</v>
       </c>
       <c r="E53" s="17" t="n">
-        <v>0.006</v>
+        <v>0.0455</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>4144200</v>
+        <v>4220600</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.83</v>
+        <v>3.76</v>
       </c>
       <c r="H53" t="n">
-        <v>69.81</v>
+        <v>43.81</v>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
@@ -2884,10 +2884,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.118</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.785</v>
+        <v>0.13</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2900,33 +2900,40 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NWEBHD</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>-0.025</v>
+        <v>0.835</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>0.006</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>4114500</v>
+        <v>4144200</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I54" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J54" s="9" t="n"/>
-      <c r="K54" s="9" t="n"/>
+        <v>0.83</v>
+      </c>
+      <c r="H54" t="n">
+        <v>69.81</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>0.785</v>
+      </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
     </row>
@@ -2938,40 +2945,33 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>NWEBHD</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>0.027</v>
+        <v>0.195</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>-0.025</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>4038100</v>
+        <v>4114500</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="H55" t="n">
-        <v>53.36</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J55" s="9" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="K55" s="9" t="n">
-        <v>0.188</v>
-      </c>
+        <v>0.18</v>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="n"/>
+      <c r="K55" s="9" t="n"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
     </row>
@@ -2983,28 +2983,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>-0.012</v>
+        <v>0.19</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>0.027</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>3905100</v>
+        <v>4075600</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="H56" t="n">
-        <v>53.76</v>
+        <v>53.36</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>4.905</v>
+        <v>0.186</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>4.804</v>
+        <v>0.188</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3028,28 +3028,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>6.71</v>
+        <v>4.94</v>
       </c>
       <c r="E57" s="10" t="n">
-        <v>-0.0219</v>
+        <v>-0.012</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3828000</v>
+        <v>3906800</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.67</v>
+        <v>0.21</v>
       </c>
       <c r="H57" t="n">
-        <v>56.94</v>
+        <v>53.76</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>6.474</v>
+        <v>4.905</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>6.075</v>
+        <v>4.804</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3073,39 +3073,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.93</v>
+        <v>6.69</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>-0.0159</v>
+        <v>-0.0248</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3579700</v>
+        <v>3863200</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.3</v>
+        <v>0.67</v>
       </c>
       <c r="H58" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="I58" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.51</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.982</v>
+        <v>6.472</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.997</v>
+        <v>6.075</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3127,19 +3127,19 @@
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="E59" s="17" t="n">
-        <v>0.04099999999999999</v>
+        <v>0.0328</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3515600</v>
+        <v>3702000</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="H59" t="n">
-        <v>44.38</v>
+        <v>43.06</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3147,10 +3147,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>1.275</v>
+        <v>1.274</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>1.46</v>
+        <v>1.459</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3163,39 +3163,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E60" s="16" t="n">
-        <v>0</v>
+        <v>0.93</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3486900</v>
+        <v>3582800</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.97</v>
+        <v>0.3</v>
       </c>
       <c r="H60" t="n">
-        <v>69.48999999999999</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.3</v>
+      </c>
+      <c r="I60" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.624</v>
+        <v>0.982</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.614</v>
+        <v>0.997</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3208,28 +3208,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>-0.0059</v>
+        <v>0.63</v>
+      </c>
+      <c r="E61" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3412500</v>
+        <v>3486900</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.43</v>
+        <v>0.97</v>
       </c>
       <c r="H61" t="n">
-        <v>55.61</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>1.639</v>
+        <v>0.624</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>1.665</v>
+        <v>0.614</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3253,39 +3253,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E62" s="16" t="n">
-        <v>0</v>
+        <v>1.68</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>-0.0059</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3357800</v>
+        <v>3425800</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="H62" t="n">
-        <v>32.68</v>
-      </c>
-      <c r="I62" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.61</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.305</v>
+        <v>1.639</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.35</v>
+        <v>1.665</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3298,28 +3298,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E63" s="16" t="n">
-        <v>0</v>
+        <v>2.64</v>
+      </c>
+      <c r="E63" s="17" t="n">
+        <v>0.0518</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3262900</v>
+        <v>3372900</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>1.63</v>
+        <v>0.83</v>
       </c>
       <c r="H63" t="n">
-        <v>50.77</v>
+        <v>61.31</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.904</v>
+        <v>2.49</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.899</v>
+        <v>2.603</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3343,28 +3343,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>-0.0476</v>
+        <v>0.28</v>
+      </c>
+      <c r="E64" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3179200</v>
+        <v>3357800</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.23</v>
+        <v>0.44</v>
       </c>
       <c r="H64" t="n">
-        <v>30.43</v>
+        <v>32.68</v>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.122</v>
+        <v>0.305</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.143</v>
+        <v>0.35</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3388,28 +3388,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>-0.0206</v>
+        <v>0.905</v>
+      </c>
+      <c r="E65" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3140200</v>
+        <v>3262900</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.49</v>
+        <v>1.63</v>
       </c>
       <c r="H65" t="n">
-        <v>42.66</v>
+        <v>50.77</v>
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
@@ -3417,10 +3417,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.49</v>
+        <v>0.904</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.509</v>
+        <v>0.899</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3442,19 +3442,19 @@
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="E66" s="17" t="n">
-        <v>0.0038</v>
+        <v>5.3</v>
+      </c>
+      <c r="E66" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3133000</v>
+        <v>3236200</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="H66" t="n">
-        <v>47.8</v>
+        <v>47.03</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>5.351</v>
+        <v>5.349</v>
       </c>
       <c r="K66" s="9" t="n">
         <v>5.539</v>
@@ -3478,28 +3478,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E67" s="17" t="n">
-        <v>0.0128</v>
+        <v>0.1</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>-0.0476</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3075900</v>
+        <v>3224200</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.58</v>
+        <v>0.23</v>
       </c>
       <c r="H67" t="n">
-        <v>41.24</v>
+        <v>30.43</v>
       </c>
       <c r="I67" s="15" t="inlineStr">
         <is>
@@ -3507,10 +3507,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.413</v>
+        <v>0.122</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.438</v>
+        <v>0.143</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3523,28 +3523,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>6.87</v>
+        <v>0.475</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>-0.0043</v>
+        <v>-0.0206</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3050700</v>
+        <v>3140200</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="H68" t="n">
-        <v>52.17</v>
+        <v>42.66</v>
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
@@ -3552,10 +3552,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>6.846</v>
+        <v>0.49</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>6.829</v>
+        <v>0.509</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3568,28 +3568,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>-0.04</v>
+        <v>0.395</v>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>0.0128</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3002700</v>
+        <v>3075900</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>1.24</v>
+        <v>0.58</v>
       </c>
       <c r="H69" t="n">
-        <v>39.95</v>
+        <v>41.24</v>
       </c>
       <c r="I69" s="15" t="inlineStr">
         <is>
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.379</v>
+        <v>0.413</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.385</v>
+        <v>0.438</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3613,28 +3613,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>0.0558</v>
+        <v>6.87</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>-0.0043</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2974900</v>
+        <v>3055300</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.73</v>
+        <v>0.52</v>
       </c>
       <c r="H70" t="n">
-        <v>61.95</v>
+        <v>52.17</v>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>2.491</v>
+        <v>6.846</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>2.604</v>
+        <v>6.829</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3658,39 +3658,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="E71" s="17" t="n">
-        <v>0.0229</v>
+        <v>0.36</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2887400</v>
+        <v>3002700</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="H71" t="n">
-        <v>66.17</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.95</v>
+      </c>
+      <c r="I71" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.645</v>
+        <v>0.379</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.633</v>
+        <v>0.385</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3703,28 +3703,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>3.93</v>
+        <v>0.665</v>
       </c>
       <c r="E72" s="17" t="n">
-        <v>0.0155</v>
+        <v>0.0153</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2859300</v>
+        <v>2965200</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.45</v>
+        <v>1.18</v>
       </c>
       <c r="H72" t="n">
-        <v>56.01</v>
+        <v>64.3</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>3.852</v>
+        <v>0.644</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>3.419</v>
+        <v>0.633</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3757,19 +3757,19 @@
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>-0.004699999999999999</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2825800</v>
+        <v>2927800</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="H73" t="n">
-        <v>67.8</v>
+        <v>66.08</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>2.018</v>
+        <v>2.017</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>1.976</v>
@@ -3793,28 +3793,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>-0.0024</v>
+        <v>3.94</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>0.0181</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2805500</v>
+        <v>2894000</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="H74" t="n">
-        <v>59.56</v>
+        <v>56.3</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
@@ -3822,10 +3822,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>4.058</v>
+        <v>3.853</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>3.728</v>
+        <v>3.419</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3838,39 +3838,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.575</v>
+        <v>4.21</v>
       </c>
       <c r="E75" s="10" t="n">
-        <v>-0.0171</v>
+        <v>-0.0024</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2713300</v>
+        <v>2847800</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="H75" t="n">
-        <v>44.03</v>
-      </c>
-      <c r="I75" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.56</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.601</v>
+        <v>4.058</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.619</v>
+        <v>3.728</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3883,28 +3883,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E76" s="16" t="n">
-        <v>0</v>
+        <v>0.575</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>-0.0171</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2701600</v>
+        <v>2749300</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1.18</v>
+        <v>0.31</v>
       </c>
       <c r="H76" t="n">
-        <v>46.5</v>
+        <v>44.03</v>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.601</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.619</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3928,28 +3928,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="E77" s="17" t="n">
-        <v>0.0219</v>
+        <v>0.555</v>
+      </c>
+      <c r="E77" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2619200</v>
+        <v>2701600</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.73</v>
+        <v>1.18</v>
       </c>
       <c r="H77" t="n">
-        <v>53.84</v>
+        <v>46.5</v>
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>2.299</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>2.231</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3973,39 +3973,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>-0.022</v>
+        <v>2.33</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>0.0219</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2421700</v>
+        <v>2649700</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.34</v>
+        <v>0.74</v>
       </c>
       <c r="H78" t="n">
-        <v>54.19</v>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.84</v>
+      </c>
+      <c r="I78" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.434</v>
+        <v>2.299</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.417</v>
+        <v>2.231</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4018,39 +4018,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0399</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E79" s="17" t="n">
-        <v>0.0263</v>
+        <v>0.445</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>-0.022</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2421000</v>
+        <v>2469200</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>1.12</v>
+        <v>0.35</v>
       </c>
       <c r="H79" t="n">
-        <v>34.41</v>
-      </c>
-      <c r="I79" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.19</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.428</v>
+        <v>0.434</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.45</v>
+        <v>0.417</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4063,28 +4063,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0399</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.605</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>-0.0397</v>
+        <v>0.39</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>0.0263</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2336700</v>
+        <v>2441000</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.9</v>
+        <v>1.13</v>
       </c>
       <c r="H80" t="n">
-        <v>40.45</v>
+        <v>34.41</v>
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.631</v>
+        <v>0.428</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.625</v>
+        <v>0.45</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4108,28 +4108,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.775</v>
+        <v>0.605</v>
       </c>
       <c r="E81" s="10" t="n">
-        <v>-0.0127</v>
+        <v>-0.0397</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2199200</v>
+        <v>2370700</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.31</v>
+        <v>0.92</v>
       </c>
       <c r="H81" t="n">
-        <v>51.24</v>
+        <v>40.45</v>
       </c>
       <c r="I81" s="15" t="inlineStr">
         <is>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.772</v>
+        <v>0.631</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.771</v>
+        <v>0.625</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4153,28 +4153,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>1.26</v>
+        <v>0.775</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0127</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2181800</v>
+        <v>2199200</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="H82" t="n">
-        <v>54.42</v>
+        <v>51.24</v>
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
@@ -4182,10 +4182,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>1.246</v>
+        <v>0.772</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>1.216</v>
+        <v>0.771</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4198,28 +4198,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E83" s="16" t="n">
-        <v>0</v>
+        <v>0.45</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>-0.0426</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2125800</v>
+        <v>2189800</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.73</v>
+        <v>0.26</v>
       </c>
       <c r="H83" t="n">
-        <v>49.59</v>
+        <v>42.73</v>
       </c>
       <c r="I83" s="15" t="inlineStr">
         <is>
@@ -4227,10 +4227,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.866</v>
+        <v>0.483</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.861</v>
+        <v>0.475</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4243,28 +4243,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E84" s="17" t="n">
-        <v>0.0062</v>
+        <v>1.25</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>-0.0157</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2114100</v>
+        <v>2184900</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.77</v>
+        <v>0.34</v>
       </c>
       <c r="H84" t="n">
-        <v>36.16</v>
+        <v>52.84</v>
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.823</v>
+        <v>1.245</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.852</v>
+        <v>1.216</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4288,39 +4288,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0222</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>OPTIMAX</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>-0.0148</v>
+        <v>0.5</v>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2079300</v>
+        <v>2150000</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.45</v>
+        <v>15.48</v>
       </c>
       <c r="H85" t="n">
-        <v>61.63</v>
-      </c>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.13</v>
+      </c>
+      <c r="I85" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.616</v>
+        <v>0.501</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.589</v>
+        <v>0.509</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4333,28 +4333,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>2.63</v>
+        <v>0.665</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>-0.0187</v>
+        <v>-0.0148</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2070000</v>
+        <v>2134100</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
       <c r="H86" t="n">
-        <v>52.05</v>
+        <v>61.63</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>2.613</v>
+        <v>0.616</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>2.597</v>
+        <v>0.589</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4378,39 +4378,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>LCTITAN</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E87" s="17" t="n">
-        <v>0.0152</v>
+        <v>0.865</v>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2063600</v>
+        <v>2125800</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>1.32</v>
+        <v>0.73</v>
       </c>
       <c r="H87" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.59</v>
+      </c>
+      <c r="I87" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.321</v>
+        <v>0.866</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.33</v>
+        <v>0.861</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4423,39 +4423,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.945</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E88" s="17" t="n">
-        <v>0.0053</v>
+        <v>0.0062</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2030200</v>
+        <v>2114100</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.46</v>
+        <v>0.77</v>
       </c>
       <c r="H88" t="n">
-        <v>58.45</v>
-      </c>
-      <c r="I88" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.16</v>
+      </c>
+      <c r="I88" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.908</v>
+        <v>0.823</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.952</v>
+        <v>0.852</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4468,39 +4468,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.45</v>
+        <v>2.62</v>
       </c>
       <c r="E89" s="10" t="n">
-        <v>-0.0426</v>
+        <v>-0.0224</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1952700</v>
+        <v>2080800</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.23</v>
+        <v>0.38</v>
       </c>
       <c r="H89" t="n">
-        <v>42.73</v>
-      </c>
-      <c r="I89" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.14</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.483</v>
+        <v>2.612</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.475</v>
+        <v>2.597</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4513,28 +4513,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>LCTITAN</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>-0.053</v>
+        <v>0.335</v>
+      </c>
+      <c r="E90" s="17" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1942400</v>
+        <v>2063600</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.36</v>
+        <v>1.32</v>
       </c>
       <c r="H90" t="n">
-        <v>57.17</v>
+        <v>57.2</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -4542,10 +4542,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.593</v>
+        <v>0.321</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.503</v>
+        <v>0.33</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4558,28 +4558,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E91" s="16" t="n">
-        <v>0</v>
+        <v>0.95</v>
+      </c>
+      <c r="E91" s="17" t="n">
+        <v>0.0106</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1931200</v>
+        <v>2035500</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.14</v>
+        <v>0.46</v>
       </c>
       <c r="H91" t="n">
-        <v>32.88</v>
+        <v>59.55</v>
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.466</v>
+        <v>0.909</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.574</v>
+        <v>0.952</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4603,39 +4603,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0395</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>OGX</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.44</v>
+        <v>0.435</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>-0.0538</v>
+        <v>-0.0114</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1905900</v>
+        <v>1972700</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.68</v>
+        <v>0.14</v>
       </c>
       <c r="H92" t="n">
-        <v>45.33</v>
-      </c>
-      <c r="I92" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>31.89</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.455</v>
+        <v>0.466</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.448</v>
+        <v>0.574</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4648,28 +4648,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>0.0147</v>
+        <v>2.88</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1872500</v>
+        <v>1947000</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.73</v>
+        <v>0.59</v>
       </c>
       <c r="H93" t="n">
-        <v>50.24</v>
+        <v>45.7</v>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
@@ -4677,10 +4677,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>1.364</v>
+        <v>2.991</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1.424</v>
+        <v>2.883</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4693,28 +4693,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5054</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TRC</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E94" s="17" t="n">
-        <v>0.0423</v>
+        <v>0.625</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>-0.053</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1861100</v>
+        <v>1944600</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>5.01</v>
+        <v>0.36</v>
       </c>
       <c r="H94" t="n">
-        <v>76.20999999999999</v>
+        <v>57.17</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -4722,10 +4722,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.322</v>
+        <v>0.593</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.301</v>
+        <v>0.503</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4738,39 +4738,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0395</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>OGX</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="E95" s="16" t="n">
-        <v>0</v>
+        <v>0.44</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>-0.0538</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1787300</v>
+        <v>1906200</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>1.42</v>
+        <v>0.68</v>
       </c>
       <c r="H95" t="n">
-        <v>45.53</v>
-      </c>
-      <c r="I95" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.33</v>
+      </c>
+      <c r="I95" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.223</v>
+        <v>0.455</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.229</v>
+        <v>0.448</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4783,28 +4783,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>-0.017</v>
+        <v>1.38</v>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1783200</v>
+        <v>1890500</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.54</v>
+        <v>0.73</v>
       </c>
       <c r="H96" t="n">
-        <v>46.09</v>
+        <v>50.24</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -4812,10 +4812,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>2.992</v>
+        <v>1.364</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>2.883</v>
+        <v>1.424</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4828,31 +4828,40 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BPROP</t>
+          <t>TRC</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E97" s="16" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>0.0423</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1724000</v>
-      </c>
-      <c r="G97" s="12" t="n"/>
-      <c r="I97" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J97" s="9" t="n"/>
-      <c r="K97" s="9" t="n"/>
+        <v>1871100</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="H97" t="n">
+        <v>76.20999999999999</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>0.301</v>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
     </row>
@@ -4864,28 +4873,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E98" s="17" t="n">
-        <v>0.0181</v>
+        <v>0.22</v>
+      </c>
+      <c r="E98" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1654200</v>
+        <v>1787300</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.66</v>
+        <v>1.42</v>
       </c>
       <c r="H98" t="n">
-        <v>64.44</v>
+        <v>45.53</v>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
@@ -4893,10 +4902,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>2.148</v>
+        <v>0.223</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>2.094</v>
+        <v>0.229</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4909,29 +4918,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>BPROP</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>-0.0276</v>
+        <v>0.25</v>
+      </c>
+      <c r="E99" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1648200</v>
-      </c>
-      <c r="G99" s="12" t="n">
-        <v>0.06</v>
-      </c>
+        <v>1724000</v>
+      </c>
+      <c r="G99" s="12" t="n"/>
       <c r="I99" s="15" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J99" s="9" t="n"/>
@@ -4947,28 +4954,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>1.26</v>
+        <v>2.25</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>0.008</v>
+        <v>0.0181</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1631900</v>
+        <v>1660200</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.25</v>
+        <v>0.67</v>
       </c>
       <c r="H100" t="n">
-        <v>47.49</v>
+        <v>64.44</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -4976,10 +4983,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>1.268</v>
+        <v>2.148</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>1.319</v>
+        <v>2.094</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4992,40 +4999,33 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="E101" s="16" t="n">
-        <v>0</v>
+        <v>0.705</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>-0.0276</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1606300</v>
+        <v>1648200</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="H101" t="n">
-        <v>40.31</v>
+        <v>0.06</v>
       </c>
       <c r="I101" s="15" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J101" s="9" t="n">
-        <v>3.101</v>
-      </c>
-      <c r="K101" s="9" t="n">
-        <v>3.224</v>
-      </c>
+      <c r="J101" s="9" t="n"/>
+      <c r="K101" s="9" t="n"/>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
     </row>
@@ -5037,28 +5037,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="E102" s="16" t="n">
-        <v>0</v>
+        <v>2.44</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>0.004099999999999999</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1588700</v>
+        <v>1636700</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.35</v>
+        <v>0.17</v>
       </c>
       <c r="H102" t="n">
-        <v>54.02</v>
+        <v>52.06</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -5066,10 +5066,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>4.488</v>
+        <v>2.431</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>4.448</v>
+        <v>2.436</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5082,28 +5082,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="E103" s="17" t="n">
-        <v>0.004099999999999999</v>
+        <v>1.25</v>
+      </c>
+      <c r="E103" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1533900</v>
+        <v>1635900</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="H103" t="n">
-        <v>52.06</v>
+        <v>45.91</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>2.431</v>
+        <v>1.267</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>2.436</v>
+        <v>1.319</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5127,28 +5127,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.25</v>
+        <v>0.215</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>-0.0196</v>
+        <v>-0.0227</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1487000</v>
+        <v>1633600</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="H104" t="n">
-        <v>42.78</v>
+        <v>40.59</v>
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.261</v>
+        <v>0.221</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.276</v>
+        <v>0.257</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5172,39 +5172,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.83</v>
+        <v>3.03</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>-0.0235</v>
+        <v>-0.0033</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1485900</v>
+        <v>1617100</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.25</v>
+        <v>0.57</v>
       </c>
       <c r="H105" t="n">
-        <v>42.55</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.5</v>
+      </c>
+      <c r="I105" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.874</v>
+        <v>3.1</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.87</v>
+        <v>3.224</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5217,28 +5217,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>-0.0177</v>
+        <v>4.57</v>
+      </c>
+      <c r="E106" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1460900</v>
+        <v>1609100</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="H106" t="n">
-        <v>52.41</v>
+        <v>54.02</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -5246,10 +5246,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>3.852</v>
+        <v>4.488</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>3.785</v>
+        <v>4.448</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5262,28 +5262,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E107" s="17" t="n">
-        <v>0.0067</v>
+        <v>0.25</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>-0.0196</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1438600</v>
+        <v>1497000</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.43</v>
+        <v>0.27</v>
       </c>
       <c r="H107" t="n">
-        <v>52.47</v>
+        <v>42.78</v>
       </c>
       <c r="I107" s="15" t="inlineStr">
         <is>
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.746</v>
+        <v>0.261</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.709</v>
+        <v>0.276</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5307,28 +5307,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="E108" s="17" t="n">
-        <v>0.0167</v>
+        <v>0.825</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>-0.0294</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1409200</v>
+        <v>1493500</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.95</v>
+        <v>0.25</v>
       </c>
       <c r="H108" t="n">
-        <v>68.40000000000001</v>
+        <v>41.94</v>
       </c>
       <c r="I108" s="13" t="inlineStr">
         <is>
@@ -5336,10 +5336,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>2.189</v>
+        <v>0.874</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>2.22</v>
+        <v>0.87</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5352,28 +5352,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.745</v>
+        <v>3.88</v>
       </c>
       <c r="E109" s="10" t="n">
-        <v>-0.0387</v>
+        <v>-0.0177</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1383400</v>
+        <v>1462100</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
       <c r="H109" t="n">
-        <v>50.84</v>
+        <v>52.41</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.749</v>
+        <v>3.852</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.702</v>
+        <v>3.785</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5397,28 +5397,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E110" s="10" t="n">
-        <v>-0.0227</v>
+        <v>0.75</v>
+      </c>
+      <c r="E110" s="17" t="n">
+        <v>0.0067</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1381200</v>
+        <v>1460500</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.15</v>
+        <v>0.43</v>
       </c>
       <c r="H110" t="n">
-        <v>40.59</v>
+        <v>52.47</v>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.221</v>
+        <v>0.746</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.257</v>
+        <v>0.709</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5442,28 +5442,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>SCGM</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E111" s="10" t="n">
-        <v>-0.0472</v>
+        <v>0.365</v>
+      </c>
+      <c r="E111" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1365600</v>
+        <v>1436800</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.26</v>
+        <v>1.84</v>
       </c>
       <c r="H111" t="n">
-        <v>59.4</v>
+        <v>66.39</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -5471,10 +5471,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>1.146</v>
+        <v>0.349</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>1.009</v>
+        <v>0.332</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5487,28 +5487,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E112" s="16" t="n">
-        <v>0</v>
+        <v>2.43</v>
+      </c>
+      <c r="E112" s="17" t="n">
+        <v>0.0125</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1358800</v>
+        <v>1419000</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.44</v>
+        <v>0.96</v>
       </c>
       <c r="H112" t="n">
-        <v>56.76</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -5516,10 +5516,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>1.271</v>
+        <v>2.188</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>1.27</v>
+        <v>2.22</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5532,39 +5532,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
         <v>1.3</v>
       </c>
-      <c r="E113" s="10" t="n">
-        <v>-0.0299</v>
+      <c r="E113" s="17" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1356700</v>
+        <v>1398700</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="H113" t="n">
-        <v>52.98</v>
-      </c>
-      <c r="I113" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.31</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>1.289</v>
+        <v>1.272</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>1.199</v>
+        <v>1.271</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5577,28 +5577,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="E114" s="17" t="n">
-        <v>0.0013</v>
+        <v>0.75</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>-0.0323</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1346500</v>
+        <v>1385900</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="H114" t="n">
-        <v>50.57</v>
+        <v>51.76</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5606,10 +5606,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>7.417</v>
+        <v>0.75</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>7.734</v>
+        <v>0.702</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5622,39 +5622,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E115" s="10" t="n">
-        <v>-0.0413</v>
+        <v>7.47</v>
+      </c>
+      <c r="E115" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1324500</v>
+        <v>1382600</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="H115" t="n">
-        <v>36.36</v>
-      </c>
-      <c r="I115" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.96</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.631</v>
+        <v>7.416</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.673</v>
+        <v>7.734</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5667,28 +5667,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="E116" s="16" t="n">
-        <v>0</v>
+        <v>1.2</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>-0.0551</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1322100</v>
+        <v>1372500</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.13</v>
+        <v>0.26</v>
       </c>
       <c r="H116" t="n">
-        <v>41.27</v>
+        <v>58.36</v>
       </c>
       <c r="I116" s="13" t="inlineStr">
         <is>
@@ -5696,10 +5696,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>6.977</v>
+        <v>1.145</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>7.414</v>
+        <v>1.009</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5712,39 +5712,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SCGM</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E117" s="16" t="n">
-        <v>0</v>
+        <v>1.29</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>-0.0373</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1319400</v>
+        <v>1371000</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>1.69</v>
+        <v>0.49</v>
       </c>
       <c r="H117" t="n">
-        <v>66.39</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.98</v>
+      </c>
+      <c r="I117" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.349</v>
+        <v>1.289</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.332</v>
+        <v>1.199</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5757,39 +5757,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E118" s="10" t="n">
-        <v>-0.0278</v>
+        <v>5.81</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1311900</v>
+        <v>1364300</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="H118" t="n">
-        <v>45.34</v>
-      </c>
-      <c r="I118" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.76</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.725</v>
+        <v>5.808</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.724</v>
+        <v>6.029</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5802,28 +5802,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="E119" s="17" t="n">
-        <v>0.0104</v>
+        <v>6.86</v>
+      </c>
+      <c r="E119" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1311700</v>
+        <v>1330600</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="H119" t="n">
-        <v>48.22</v>
+        <v>41.27</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5831,10 +5831,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>5.81</v>
+        <v>6.977</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>6.029</v>
+        <v>7.414</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5856,19 +5856,19 @@
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>-0.0172</v>
+        <v>-0.0259</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1311400</v>
+        <v>1326500</v>
       </c>
       <c r="G120" s="12" t="n">
         <v>0.44</v>
       </c>
       <c r="H120" t="n">
-        <v>55.82</v>
+        <v>54.62</v>
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>1.114</v>
+        <v>1.113</v>
       </c>
       <c r="K120" s="9" t="n">
         <v>0.964</v>
@@ -5892,39 +5892,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.61</v>
+        <v>0.58</v>
       </c>
       <c r="E121" s="10" t="n">
-        <v>-0.0123</v>
+        <v>-0.0413</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1246200</v>
+        <v>1324600</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="H121" t="n">
-        <v>44.14</v>
-      </c>
-      <c r="I121" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.36</v>
+      </c>
+      <c r="I121" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>1.645</v>
+        <v>0.631</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>1.727</v>
+        <v>0.673</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5937,39 +5937,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E122" s="17" t="n">
-        <v>0.0192</v>
+        <v>0.7</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1220300</v>
+        <v>1312200</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="H122" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="I122" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.34</v>
+      </c>
+      <c r="I122" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.267</v>
+        <v>0.725</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.287</v>
+        <v>0.724</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1196700</v>
+        <v>1308400</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="H123" t="n">
         <v>58.74</v>
@@ -6027,28 +6027,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>7.39</v>
+        <v>1.6</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>-0.0327</v>
+        <v>-0.0184</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1175400</v>
+        <v>1284300</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="H124" t="n">
-        <v>52.2</v>
+        <v>43.24</v>
       </c>
       <c r="I124" s="13" t="inlineStr">
         <is>
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>7.363</v>
+        <v>1.644</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>7.011</v>
+        <v>1.727</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6072,28 +6072,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>-0.0391</v>
+        <v>0.265</v>
+      </c>
+      <c r="E125" s="17" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1164300</v>
+        <v>1245300</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="H125" t="n">
-        <v>63.02</v>
+        <v>44.9</v>
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
@@ -6101,10 +6101,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.267</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.498</v>
+        <v>0.287</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6117,39 +6117,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0222</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>OPTIMAX</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E126" s="16" t="n">
-        <v>0</v>
+        <v>0.615</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>-0.0391</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1150000</v>
+        <v>1211400</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>8.279999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="H126" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I126" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.02</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.501</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.509</v>
+        <v>0.498</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6162,39 +6162,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2.05</v>
+        <v>7.41</v>
       </c>
       <c r="E127" s="10" t="n">
-        <v>-0.0049</v>
+        <v>-0.0301</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1141400</v>
+        <v>1177900</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="H127" t="n">
-        <v>51.53</v>
-      </c>
-      <c r="I127" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.67</v>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>2.04</v>
+        <v>7.365</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>2.058</v>
+        <v>7.011</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6222,10 +6222,10 @@
         <v>0</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1113400</v>
+        <v>1153300</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="H128" t="n">
         <v>60.27</v>
@@ -6252,39 +6252,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>1.26</v>
+        <v>0.625</v>
       </c>
       <c r="E129" s="10" t="n">
-        <v>-0.0156</v>
+        <v>-0.0157</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1113300</v>
+        <v>1151100</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="H129" t="n">
-        <v>21.38</v>
-      </c>
-      <c r="I129" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.52</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>1.394</v>
+        <v>0.668</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>1.444</v>
+        <v>0.726</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6297,39 +6297,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.62</v>
+        <v>2.04</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>-0.0236</v>
+        <v>-0.0097</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1104900</v>
+        <v>1147300</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="H130" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.37</v>
+      </c>
+      <c r="I130" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.668</v>
+        <v>2.039</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.726</v>
+        <v>2.057</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6342,39 +6342,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.59</v>
+        <v>1.26</v>
       </c>
       <c r="E131" s="10" t="n">
-        <v>-0.0328</v>
+        <v>-0.0156</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1057700</v>
+        <v>1119800</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.21</v>
+        <v>0.26</v>
       </c>
       <c r="H131" t="n">
-        <v>56.67</v>
-      </c>
-      <c r="I131" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.38</v>
+      </c>
+      <c r="I131" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.394</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.535</v>
+        <v>1.444</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6387,28 +6387,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>VANTNRG</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="E132" s="10" t="n">
-        <v>-0.017</v>
+        <v>0.29</v>
+      </c>
+      <c r="E132" s="17" t="n">
+        <v>0.0175</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1053500</v>
+        <v>1077900</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.24</v>
+        <v>0.73</v>
       </c>
       <c r="H132" t="n">
-        <v>57.12</v>
+        <v>36.16</v>
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>5.601</v>
+        <v>0.304</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>5.409</v>
+        <v>0.324</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6432,39 +6432,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E133" s="16" t="n">
-        <v>0</v>
+        <v>5.79</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>-0.017</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1032400</v>
+        <v>1063500</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.49</v>
+        <v>0.24</v>
       </c>
       <c r="H133" t="n">
-        <v>68.51000000000001</v>
-      </c>
-      <c r="I133" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.12</v>
+      </c>
+      <c r="I133" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>1.388</v>
+        <v>5.601</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>1.357</v>
+        <v>5.409</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6477,39 +6477,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>VANTNRG</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E134" s="17" t="n">
-        <v>0.0175</v>
+        <v>0.59</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>-0.0328</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1025700</v>
+        <v>1057700</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.7</v>
+        <v>0.21</v>
       </c>
       <c r="H134" t="n">
-        <v>36.16</v>
-      </c>
-      <c r="I134" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.67</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.304</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.324</v>
+        <v>0.535</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6522,39 +6522,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>-0.0392</v>
+        <v>1.43</v>
+      </c>
+      <c r="E135" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1025000</v>
+        <v>1032400</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.16</v>
+        <v>0.49</v>
       </c>
       <c r="H135" t="n">
-        <v>28.26</v>
-      </c>
-      <c r="I135" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.51000000000001</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.263</v>
+        <v>1.388</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.268</v>
+        <v>1.357</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6567,28 +6567,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.42</v>
+        <v>0.245</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>-0.0118</v>
+        <v>-0.0392</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1006300</v>
+        <v>1027600</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H136" t="n">
-        <v>55.32</v>
+        <v>28.26</v>
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
@@ -6596,10 +6596,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.407</v>
+        <v>0.263</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.37</v>
+        <v>0.268</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6627,10 +6627,10 @@
         <v>-0.0119</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>993200</v>
+        <v>1025000</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H137" t="n">
         <v>36.07</v>
@@ -6657,39 +6657,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0336</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>WINSTAR</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E138" s="17" t="n">
-        <v>0.008</v>
+        <v>0.42</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>977700</v>
+        <v>1011300</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>1.96</v>
+        <v>0.15</v>
       </c>
       <c r="H138" t="n">
-        <v>39.89</v>
-      </c>
-      <c r="I138" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.32</v>
+      </c>
+      <c r="I138" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.634</v>
+        <v>0.407</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.648</v>
+        <v>0.37</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6702,28 +6702,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>0336</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CITAGLB</t>
+          <t>WINSTAR</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>1.16</v>
+        <v>0.63</v>
       </c>
       <c r="E139" s="17" t="n">
-        <v>0.045</v>
+        <v>0.008</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>967700</v>
+        <v>977700</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>3.87</v>
+        <v>1.96</v>
       </c>
       <c r="H139" t="n">
-        <v>67.01000000000001</v>
+        <v>39.89</v>
       </c>
       <c r="I139" s="13" t="inlineStr">
         <is>
@@ -6731,10 +6731,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>1.064</v>
+        <v>0.634</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>1.051</v>
+        <v>0.648</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6747,28 +6747,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>CITAGLB</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E140" s="10" t="n">
-        <v>-0.0144</v>
+        <v>1.16</v>
+      </c>
+      <c r="E140" s="17" t="n">
+        <v>0.045</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>962700</v>
+        <v>967800</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.19</v>
+        <v>3.87</v>
       </c>
       <c r="H140" t="n">
-        <v>38.98</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="I140" s="13" t="inlineStr">
         <is>
@@ -6776,10 +6776,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>0.706</v>
+        <v>1.064</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.757</v>
+        <v>1.051</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6792,28 +6792,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>2.44</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E141" s="10" t="n">
-        <v>-0.024</v>
+        <v>-0.0144</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>960200</v>
+        <v>962700</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="H141" t="n">
-        <v>39.97</v>
+        <v>38.98</v>
       </c>
       <c r="I141" s="13" t="inlineStr">
         <is>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>2.602</v>
+        <v>0.706</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>2.798</v>
+        <v>0.757</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6837,39 +6837,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E142" s="16" t="n">
-        <v>0</v>
+        <v>2.46</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>-0.016</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>930400</v>
+        <v>960900</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>1.49</v>
+        <v>0.16</v>
       </c>
       <c r="H142" t="n">
-        <v>51.68</v>
-      </c>
-      <c r="I142" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.71</v>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>1.011</v>
+        <v>2.604</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>0.992</v>
+        <v>2.799</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6897,10 +6897,10 @@
         <v>-0.09420000000000001</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>909800</v>
+        <v>952400</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>6.69</v>
+        <v>7</v>
       </c>
       <c r="H143" t="n">
         <v>25.15</v>
@@ -6927,28 +6927,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E144" s="10" t="n">
-        <v>-0.03759999999999999</v>
+        <v>1.01</v>
+      </c>
+      <c r="E144" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>901800</v>
+        <v>930400</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.2</v>
+        <v>1.49</v>
       </c>
       <c r="H144" t="n">
-        <v>40.57</v>
+        <v>51.68</v>
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>0.697</v>
+        <v>1.011</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.992</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6972,39 +6972,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="E145" s="10" t="n">
-        <v>-0.02</v>
+        <v>4.43</v>
+      </c>
+      <c r="E145" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>900400</v>
+        <v>925000</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
       <c r="H145" t="n">
-        <v>56.36</v>
-      </c>
-      <c r="I145" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.96</v>
+      </c>
+      <c r="I145" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>10.621</v>
+        <v>4.519</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>9.999000000000001</v>
+        <v>4.641</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7032,10 +7032,10 @@
         <v>-0.0165</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>898800</v>
+        <v>907500</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H146" t="n">
         <v>17.99</v>
@@ -7062,39 +7062,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E147" s="16" t="n">
-        <v>0</v>
+        <v>0.645</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>-0.0301</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>896000</v>
+        <v>903300</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.91</v>
+        <v>0.2</v>
       </c>
       <c r="H147" t="n">
-        <v>58.13</v>
-      </c>
-      <c r="I147" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.17</v>
+      </c>
+      <c r="I147" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>0.636</v>
+        <v>0.698</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>0.634</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7107,28 +7107,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E148" s="16" t="n">
-        <v>0</v>
+        <v>10.8</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>873100</v>
+        <v>902200</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.6</v>
+        <v>0.24</v>
       </c>
       <c r="H148" t="n">
-        <v>38.22</v>
+        <v>56.36</v>
       </c>
       <c r="I148" s="13" t="inlineStr">
         <is>
@@ -7136,10 +7136,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>0.915</v>
+        <v>10.621</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>0.972</v>
+        <v>9.999000000000001</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7152,39 +7152,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E149" s="10" t="n">
-        <v>-0.0074</v>
+        <v>0.64</v>
+      </c>
+      <c r="E149" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>863700</v>
+        <v>896000</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.24</v>
+        <v>0.91</v>
       </c>
       <c r="H149" t="n">
-        <v>40.72</v>
-      </c>
-      <c r="I149" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.13</v>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>2.797</v>
+        <v>0.636</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>2.929</v>
+        <v>0.634</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7197,39 +7197,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>1.23</v>
+        <v>2.7</v>
       </c>
       <c r="E150" s="10" t="n">
-        <v>-0.0538</v>
+        <v>-0.0074</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>845900</v>
+        <v>879600</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.46</v>
+        <v>0.25</v>
       </c>
       <c r="H150" t="n">
-        <v>42.54</v>
-      </c>
-      <c r="I150" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.72</v>
+      </c>
+      <c r="I150" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>1.291</v>
+        <v>2.797</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>1.315</v>
+        <v>2.929</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7242,28 +7242,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E151" s="10" t="n">
-        <v>-0.016</v>
+        <v>0.895</v>
+      </c>
+      <c r="E151" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>822300</v>
+        <v>873100</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.23</v>
+        <v>0.6</v>
       </c>
       <c r="H151" t="n">
-        <v>49.73</v>
+        <v>38.22</v>
       </c>
       <c r="I151" s="13" t="inlineStr">
         <is>
@@ -7271,10 +7271,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>1.253</v>
+        <v>0.915</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>1.142</v>
+        <v>0.972</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7287,28 +7287,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>5.16</v>
+        <v>1.23</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>-0.0039</v>
+        <v>-0.016</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>802100</v>
+        <v>872300</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="H152" t="n">
-        <v>54.84</v>
+        <v>49.73</v>
       </c>
       <c r="I152" s="13" t="inlineStr">
         <is>
@@ -7316,10 +7316,10 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>5.088</v>
+        <v>1.253</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>5.033</v>
+        <v>1.142</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7332,28 +7332,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>1.75</v>
+        <v>1.23</v>
       </c>
       <c r="E153" s="10" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0538</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>795300</v>
+        <v>845900</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.27</v>
+        <v>0.46</v>
       </c>
       <c r="H153" t="n">
-        <v>46.11</v>
+        <v>42.54</v>
       </c>
       <c r="I153" s="13" t="inlineStr">
         <is>
@@ -7361,10 +7361,10 @@
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>1.758</v>
+        <v>1.291</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>1.832</v>
+        <v>1.315</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7377,28 +7377,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>PANTECH</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>0.6850000000000001</v>
+        <v>5.15</v>
       </c>
       <c r="E154" s="10" t="n">
-        <v>-0.0072</v>
+        <v>-0.0058</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>778600</v>
+        <v>840700</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="H154" t="n">
-        <v>64.13</v>
+        <v>54.25</v>
       </c>
       <c r="I154" s="13" t="inlineStr">
         <is>
@@ -7406,10 +7406,10 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>0.665</v>
+        <v>5.087</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>0.662</v>
+        <v>5.033</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7422,39 +7422,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>TMK</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E155" s="10" t="n">
-        <v>-0.0098</v>
+        <v>3.2</v>
+      </c>
+      <c r="E155" s="17" t="n">
+        <v>0.0159</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>768500</v>
+        <v>820100</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.22</v>
+        <v>0.74</v>
       </c>
       <c r="H155" t="n">
-        <v>35.99</v>
-      </c>
-      <c r="I155" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.73</v>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>0.521</v>
+        <v>2.894</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>0.552</v>
+        <v>2.867</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7467,28 +7467,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0293</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>KJTS</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="E156" s="17" t="n">
-        <v>0.0104</v>
+        <v>1.75</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>758800</v>
+        <v>796600</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.73</v>
+        <v>0.27</v>
       </c>
       <c r="H156" t="n">
-        <v>54.79</v>
+        <v>46.11</v>
       </c>
       <c r="I156" s="13" t="inlineStr">
         <is>
@@ -7496,10 +7496,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>0.9409999999999999</v>
+        <v>1.758</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>0.999</v>
+        <v>1.832</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7512,28 +7512,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>PANTECH</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>1.57</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E157" s="16" t="n">
         <v>0</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>742300</v>
+        <v>788600</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.92</v>
+        <v>1.83</v>
       </c>
       <c r="H157" t="n">
-        <v>32.37</v>
+        <v>68.33</v>
       </c>
       <c r="I157" s="13" t="inlineStr">
         <is>
@@ -7541,10 +7541,10 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>1.672</v>
+        <v>0.665</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>1.752</v>
+        <v>0.662</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7557,28 +7557,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>3.16</v>
+        <v>0.505</v>
       </c>
       <c r="E158" s="10" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.0098</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>739000</v>
+        <v>788500</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="H158" t="n">
-        <v>36.77</v>
+        <v>35.99</v>
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
@@ -7586,10 +7586,10 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>3.266</v>
+        <v>0.521</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>3.491</v>
+        <v>0.552</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7602,28 +7602,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>0293</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>KJTS</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E159" s="16" t="n">
-        <v>0</v>
+        <v>0.975</v>
+      </c>
+      <c r="E159" s="17" t="n">
+        <v>0.0104</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>695100</v>
+        <v>768800</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.47</v>
+        <v>0.74</v>
       </c>
       <c r="H159" t="n">
-        <v>60.22</v>
+        <v>54.79</v>
       </c>
       <c r="I159" s="13" t="inlineStr">
         <is>
@@ -7631,10 +7631,10 @@
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>0.619</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>0.554</v>
+        <v>0.999</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7647,39 +7647,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E160" s="17" t="n">
-        <v>0.004</v>
+        <v>3.15</v>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>-0.0125</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>691700</v>
+        <v>766300</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="H160" t="n">
-        <v>47.11</v>
-      </c>
-      <c r="I160" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.17</v>
+      </c>
+      <c r="I160" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>2.511</v>
+        <v>3.265</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>2.615</v>
+        <v>3.491</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7692,39 +7692,39 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>HI</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E161" s="17" t="n">
-        <v>0.005</v>
+        <v>1.57</v>
+      </c>
+      <c r="E161" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>675000</v>
+        <v>742300</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.27</v>
+        <v>0.92</v>
       </c>
       <c r="H161" t="n">
-        <v>37.77</v>
-      </c>
-      <c r="I161" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>32.37</v>
+      </c>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>1.044</v>
+        <v>1.672</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>1.106</v>
+        <v>1.752</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7737,39 +7737,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="E162" s="17" t="n">
-        <v>0.0023</v>
+        <v>2.5</v>
+      </c>
+      <c r="E162" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>660900</v>
+        <v>723200</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="H162" t="n">
-        <v>36.54</v>
-      </c>
-      <c r="I162" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.78</v>
+      </c>
+      <c r="I162" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>4.52</v>
+        <v>2.51</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>4.641</v>
+        <v>2.615</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7782,28 +7782,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>BAUTO</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E163" s="10" t="n">
-        <v>-0.005600000000000001</v>
+        <v>0.635</v>
+      </c>
+      <c r="E163" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>653200</v>
+        <v>695100</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="H163" t="n">
-        <v>45.84</v>
+        <v>60.22</v>
       </c>
       <c r="I163" s="13" t="inlineStr">
         <is>
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>0.887</v>
+        <v>0.619</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>0.899</v>
+        <v>0.554</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7827,39 +7827,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5109</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>YTLREIT</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="E164" s="17" t="n">
-        <v>0.0053</v>
+        <v>0.955</v>
+      </c>
+      <c r="E164" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>636300</v>
+        <v>690500</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.21</v>
+        <v>1.47</v>
       </c>
       <c r="H164" t="n">
-        <v>51.46</v>
-      </c>
-      <c r="I164" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.6</v>
+      </c>
+      <c r="I164" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>7.582</v>
+        <v>0.968</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>7.666</v>
+        <v>0.987</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7872,28 +7872,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E165" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E165" s="17" t="n">
+        <v>0.005</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>626400</v>
+        <v>689100</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="H165" t="n">
-        <v>26.97</v>
+        <v>37.77</v>
       </c>
       <c r="I165" s="15" t="inlineStr">
         <is>
@@ -7901,10 +7901,10 @@
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>0.851</v>
+        <v>1.044</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>1.009</v>
+        <v>1.106</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7917,28 +7917,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>OSK</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="E166" s="10" t="n">
-        <v>-0.0062</v>
+        <v>0.79</v>
+      </c>
+      <c r="E166" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>619100</v>
+        <v>665100</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.5</v>
+        <v>0.31</v>
       </c>
       <c r="H166" t="n">
-        <v>32.55</v>
+        <v>26.97</v>
       </c>
       <c r="I166" s="15" t="inlineStr">
         <is>
@@ -7946,10 +7946,10 @@
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>1.663</v>
+        <v>0.851</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>1.808</v>
+        <v>1.009</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7962,28 +7962,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>BAUTO</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>3.19</v>
+        <v>0.88</v>
       </c>
       <c r="E167" s="10" t="n">
-        <v>-0.0062</v>
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>614300</v>
+        <v>662300</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.47</v>
+        <v>0.36</v>
       </c>
       <c r="H167" t="n">
-        <v>54.65</v>
+        <v>45.84</v>
       </c>
       <c r="I167" s="13" t="inlineStr">
         <is>
@@ -7991,10 +7991,10 @@
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>3.172</v>
+        <v>0.887</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>3.006</v>
+        <v>0.899</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8007,39 +8007,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E168" s="16" t="n">
-        <v>0</v>
+        <v>7.62</v>
+      </c>
+      <c r="E168" s="17" t="n">
+        <v>0.0053</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>607000</v>
+        <v>646500</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>1.02</v>
+        <v>0.22</v>
       </c>
       <c r="H168" t="n">
-        <v>49.92</v>
-      </c>
-      <c r="I168" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.46</v>
+      </c>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>0.6830000000000001</v>
+        <v>7.582</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>0.666</v>
+        <v>7.666</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8052,39 +8052,39 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="E169" s="16" t="n">
-        <v>0</v>
+        <v>3.18</v>
+      </c>
+      <c r="E169" s="10" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>581100</v>
+        <v>627300</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>0.26</v>
+        <v>0.48</v>
       </c>
       <c r="H169" t="n">
-        <v>58.43</v>
-      </c>
-      <c r="I169" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.72</v>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>0.662</v>
+        <v>3.171</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>0.596</v>
+        <v>3.006</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8097,39 +8097,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0168</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>BMGREEN</t>
+          <t>OSK</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="E170" s="10" t="n">
-        <v>-0.0203</v>
+        <v>-0.0123</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>580300</v>
+        <v>624300</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="H170" t="n">
-        <v>45.12</v>
-      </c>
-      <c r="I170" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.3</v>
+      </c>
+      <c r="I170" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>1.466</v>
+        <v>1.662</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>1.569</v>
+        <v>1.807</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8142,39 +8142,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0326</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SORENTO</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="E171" s="10" t="n">
-        <v>-0.0053</v>
+        <v>0.68</v>
+      </c>
+      <c r="E171" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>555500</v>
+        <v>607000</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.12</v>
+        <v>1.02</v>
       </c>
       <c r="H171" t="n">
-        <v>38.26</v>
-      </c>
-      <c r="I171" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.92</v>
+      </c>
+      <c r="I171" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>0.948</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>1.019</v>
+        <v>0.666</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8187,39 +8187,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="E172" s="17" t="n">
-        <v>0.009300000000000001</v>
+        <v>1.07</v>
+      </c>
+      <c r="E172" s="10" t="n">
+        <v>-0.0183</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>550500</v>
+        <v>605500</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="H172" t="n">
-        <v>47.52</v>
-      </c>
-      <c r="I172" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.73</v>
+      </c>
+      <c r="I172" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>4.329</v>
+        <v>1.11</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>4.563</v>
+        <v>1.116</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8232,39 +8232,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>3.07</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E173" s="10" t="n">
-        <v>-0.0032</v>
+        <v>-0.0053</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>540600</v>
+        <v>585200</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="H173" t="n">
-        <v>64.25</v>
-      </c>
-      <c r="I173" s="15" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.26</v>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>2.906</v>
+        <v>0.948</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>2.464</v>
+        <v>1.019</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8277,28 +8277,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>0277</t>
+          <t>0168</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>CLOUDPT</t>
+          <t>BMGREEN</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E174" s="16" t="n">
-        <v>0</v>
+        <v>1.46</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>-0.0135</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>515700</v>
+        <v>582400</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.19</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H174" t="n">
-        <v>55.74</v>
+        <v>46.13</v>
       </c>
       <c r="I174" s="13" t="inlineStr">
         <is>
@@ -8306,10 +8306,10 @@
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>0.495</v>
+        <v>1.467</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>0.485</v>
+        <v>1.569</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8322,45 +8322,315 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E175" s="10" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.68</v>
+      </c>
+      <c r="E175" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>502000</v>
+        <v>581100</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.08</v>
+        <v>0.26</v>
       </c>
       <c r="H175" t="n">
-        <v>53.19</v>
-      </c>
-      <c r="I175" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.43</v>
+      </c>
+      <c r="I175" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>2.825</v>
+        <v>0.662</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>2.717</v>
+        <v>0.596</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
     </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>0277</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>CLOUDPT</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E176" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>578000</v>
+      </c>
+      <c r="G176" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H176" t="n">
+        <v>55.74</v>
+      </c>
+      <c r="I176" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J176" s="9" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="K176" s="9" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="14" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E177" s="17" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>562800</v>
+      </c>
+      <c r="G177" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H177" t="n">
+        <v>46.77</v>
+      </c>
+      <c r="I177" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="n">
+        <v>4.328</v>
+      </c>
+      <c r="K177" s="9" t="n">
+        <v>4.563</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="14" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E178" s="10" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>549700</v>
+      </c>
+      <c r="G178" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H178" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="I178" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J178" s="9" t="n">
+        <v>2.906</v>
+      </c>
+      <c r="K178" s="9" t="n">
+        <v>2.464</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="14" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E179" s="10" t="n">
+        <v>-0.0347</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>527000</v>
+      </c>
+      <c r="G179" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H179" t="n">
+        <v>42.41</v>
+      </c>
+      <c r="I179" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J179" s="9" t="n">
+        <v>1.017</v>
+      </c>
+      <c r="K179" s="9" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="14" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>5321</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>KEYFIELD</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E180" s="17" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>507200</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H180" t="n">
+        <v>52.71</v>
+      </c>
+      <c r="I180" s="15" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J180" s="9" t="n">
+        <v>1.388</v>
+      </c>
+      <c r="K180" s="9" t="n">
+        <v>1.376</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="14" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E181" s="10" t="n">
+        <v>-0.006999999999999999</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>507000</v>
+      </c>
+      <c r="G181" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H181" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="I181" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J181" s="9" t="n">
+        <v>2.825</v>
+      </c>
+      <c r="K181" s="9" t="n">
+        <v>2.717</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M175"/>
+  <autoFilter ref="A1:M181"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>